--- a/dados/fonte/Book_3_1.xlsx
+++ b/dados/fonte/Book_3_1.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEBE289C-984B-4CE5-9B92-D374407FC793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C98F4725-3FEA-42D2-80B0-DFDBD5238D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Times" sheetId="1" r:id="rId1"/>
@@ -33,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2616" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2754" uniqueCount="949">
   <si>
     <t>Nome Abreviado</t>
   </si>
@@ -2520,13 +2525,373 @@
   </si>
   <si>
     <t>npcs por quarteirão</t>
+  </si>
+  <si>
+    <t>TGA</t>
+  </si>
+  <si>
+    <t>ULTRAS</t>
+  </si>
+  <si>
+    <t>RAÇA</t>
+  </si>
+  <si>
+    <t>ESQUADRÃO</t>
+  </si>
+  <si>
+    <t>DRAGÕES</t>
+  </si>
+  <si>
+    <t>FALANGE</t>
+  </si>
+  <si>
+    <t>TRA</t>
+  </si>
+  <si>
+    <t>TIM</t>
+  </si>
+  <si>
+    <t>TMA</t>
+  </si>
+  <si>
+    <t>TSA</t>
+  </si>
+  <si>
+    <t>TSV</t>
+  </si>
+  <si>
+    <t>TMV</t>
+  </si>
+  <si>
+    <t>TEA</t>
+  </si>
+  <si>
+    <t>TFB</t>
+  </si>
+  <si>
+    <t>IMPERIO</t>
+  </si>
+  <si>
+    <t>TOMN</t>
+  </si>
+  <si>
+    <t>ESQUAD</t>
+  </si>
+  <si>
+    <t>GALOUC</t>
+  </si>
+  <si>
+    <t>TOF</t>
+  </si>
+  <si>
+    <t>TOG</t>
+  </si>
+  <si>
+    <t>TOB</t>
+  </si>
+  <si>
+    <t>TOC</t>
+  </si>
+  <si>
+    <t>U92</t>
+  </si>
+  <si>
+    <t>TODA</t>
+  </si>
+  <si>
+    <t>TOMA</t>
+  </si>
+  <si>
+    <t>TOTT</t>
+  </si>
+  <si>
+    <t>TSB</t>
+  </si>
+  <si>
+    <t>FJB</t>
+  </si>
+  <si>
+    <t>TJB</t>
+  </si>
+  <si>
+    <t>FFT</t>
+  </si>
+  <si>
+    <t>CRN</t>
+  </si>
+  <si>
+    <t>FJBA</t>
+  </si>
+  <si>
+    <t>FURIAPB</t>
+  </si>
+  <si>
+    <t>TJBPB</t>
+  </si>
+  <si>
+    <t>TGL</t>
+  </si>
+  <si>
+    <t>TFJ</t>
+  </si>
+  <si>
+    <t>TCA</t>
+  </si>
+  <si>
+    <t>GAVIOES</t>
+  </si>
+  <si>
+    <t>TJF</t>
+  </si>
+  <si>
+    <t>CMA</t>
+  </si>
+  <si>
+    <t>FORÇA</t>
+  </si>
+  <si>
+    <t>MV</t>
+  </si>
+  <si>
+    <t>FJV</t>
+  </si>
+  <si>
+    <t>TJG</t>
+  </si>
+  <si>
+    <t>FJG</t>
+  </si>
+  <si>
+    <t>IJG</t>
+  </si>
+  <si>
+    <t>TTI</t>
+  </si>
+  <si>
+    <t>TUF</t>
+  </si>
+  <si>
+    <t>TOIC</t>
+  </si>
+  <si>
+    <t>TJS</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>TUTB</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>IAV</t>
+  </si>
+  <si>
+    <t>TYF</t>
+  </si>
+  <si>
+    <t>TJFAN</t>
+  </si>
+  <si>
+    <t>TEV</t>
+  </si>
+  <si>
+    <t>TUI</t>
+  </si>
+  <si>
+    <t>TOCV</t>
+  </si>
+  <si>
+    <t>TOCA</t>
+  </si>
+  <si>
+    <t>TFI</t>
+  </si>
+  <si>
+    <t>TJP</t>
+  </si>
+  <si>
+    <t>MVJ</t>
+  </si>
+  <si>
+    <t>OT</t>
+  </si>
+  <si>
+    <t>SRG</t>
+  </si>
+  <si>
+    <t>UT</t>
+  </si>
+  <si>
+    <t>IJV</t>
+  </si>
+  <si>
+    <t>TFI HSG</t>
+  </si>
+  <si>
+    <t>P9</t>
+  </si>
+  <si>
+    <t>TTA</t>
+  </si>
+  <si>
+    <t>TTF</t>
+  </si>
+  <si>
+    <t>TOGA</t>
+  </si>
+  <si>
+    <t>TEC</t>
+  </si>
+  <si>
+    <t>TPI</t>
+  </si>
+  <si>
+    <t>NAÇÃO</t>
+  </si>
+  <si>
+    <t>GANG</t>
+  </si>
+  <si>
+    <t>TFA</t>
+  </si>
+  <si>
+    <t>JGT</t>
+  </si>
+  <si>
+    <t>TJC</t>
+  </si>
+  <si>
+    <t>FJP</t>
+  </si>
+  <si>
+    <t>FJY</t>
+  </si>
+  <si>
+    <t>MY</t>
+  </si>
+  <si>
+    <t>TUMF</t>
+  </si>
+  <si>
+    <t>NARRAÇA</t>
+  </si>
+  <si>
+    <t>INTERROR</t>
+  </si>
+  <si>
+    <t>TJT</t>
+  </si>
+  <si>
+    <t>SJS</t>
+  </si>
+  <si>
+    <t>TJSALG</t>
+  </si>
+  <si>
+    <t>TEG</t>
+  </si>
+  <si>
+    <t>TFF</t>
+  </si>
+  <si>
+    <t>GARRA</t>
+  </si>
+  <si>
+    <t>GAVIR</t>
+  </si>
+  <si>
+    <t>INDEP</t>
+  </si>
+  <si>
+    <t>UF</t>
+  </si>
+  <si>
+    <t>LEOES</t>
+  </si>
+  <si>
+    <t>TOP6</t>
+  </si>
+  <si>
+    <t>JÁGUIA</t>
+  </si>
+  <si>
+    <t>JBARRA</t>
+  </si>
+  <si>
+    <t>DRAGOES</t>
+  </si>
+  <si>
+    <t>ALIANCA</t>
+  </si>
+  <si>
+    <t>TGT</t>
+  </si>
+  <si>
+    <t>TFL</t>
+  </si>
+  <si>
+    <t>BOCSUJ</t>
+  </si>
+  <si>
+    <t>RAÇTRI</t>
+  </si>
+  <si>
+    <t>SANGRU</t>
+  </si>
+  <si>
+    <t>GARTI</t>
+  </si>
+  <si>
+    <t>TIV</t>
+  </si>
+  <si>
+    <t>TDF</t>
+  </si>
+  <si>
+    <t>TFT</t>
+  </si>
+  <si>
+    <t>POEIRAZ</t>
+  </si>
+  <si>
+    <t>C12VIT</t>
+  </si>
+  <si>
+    <t>TJVOLT</t>
+  </si>
+  <si>
+    <t>FJC</t>
+  </si>
+  <si>
+    <t>MUC</t>
+  </si>
+  <si>
+    <t>FRV</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>OSFARR</t>
+  </si>
+  <si>
+    <t>FURIA</t>
+  </si>
+  <si>
+    <t>JOVEMFLO</t>
+  </si>
+  <si>
+    <t>SANGAZ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2741,7 +3106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2796,6 +3161,10 @@
       <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2834,6 +3203,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{46417444-F3C7-4E17-B86D-413BE63F94EC}" name="Tabela1" displayName="Tabela1" ref="A1:R109" totalsRowShown="0">
   <autoFilter ref="A1:R109" xr:uid="{46417444-F3C7-4E17-B86D-413BE63F94EC}"/>
@@ -2865,10 +3238,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4B04D8F-8565-4F76-BD12-C944E7E685F1}" name="Tabela2" displayName="Tabela2" ref="A1:H139" totalsRowShown="0">
-  <autoFilter ref="A1:H139" xr:uid="{A4B04D8F-8565-4F76-BD12-C944E7E685F1}"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4B04D8F-8565-4F76-BD12-C944E7E685F1}" name="Tabela2" displayName="Tabela2" ref="A1:I139" totalsRowShown="0">
+  <autoFilter ref="A1:I139" xr:uid="{A4B04D8F-8565-4F76-BD12-C944E7E685F1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I139">
+    <sortCondition descending="1" ref="I1:I139"/>
+  </sortState>
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{67D8D6CE-74E9-4B1A-A971-D641A94CA200}" name="Torcida"/>
+    <tableColumn id="9" xr3:uid="{A80A4DFF-C6AE-401C-B7A2-D423DDAEA0C6}" name="Sigla"/>
     <tableColumn id="8" xr3:uid="{3B22972F-D26F-491F-A5D2-F791479D329B}" name="Data de fundação"/>
     <tableColumn id="2" xr3:uid="{9B5066FB-1024-4E23-97E3-8FD4B1C70240}" name="Time"/>
     <tableColumn id="3" xr3:uid="{D38C39D3-B19E-47E4-9066-F6D0CD21BD81}" name="Mapa"/>
@@ -2882,9 +3259,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2922,7 +3299,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3028,7 +3405,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3170,7 +3547,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3179,7 +3556,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T109"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="19.42578125" customWidth="1"/>
     <col min="15" max="15" width="21.42578125" customWidth="1"/>
@@ -3187,7 +3564,7 @@
     <col min="18" max="18" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3246,7 +3623,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -3305,7 +3682,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -3364,7 +3741,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -3423,7 +3800,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>53</v>
       </c>
@@ -3482,7 +3859,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -3541,7 +3918,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>71</v>
       </c>
@@ -3600,7 +3977,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>78</v>
       </c>
@@ -3659,7 +4036,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>85</v>
       </c>
@@ -3715,7 +4092,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>93</v>
       </c>
@@ -3771,7 +4148,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>98</v>
       </c>
@@ -3827,7 +4204,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>104</v>
       </c>
@@ -3883,7 +4260,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -3939,7 +4316,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>120</v>
       </c>
@@ -3995,7 +4372,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>128</v>
       </c>
@@ -4051,7 +4428,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>136</v>
       </c>
@@ -4107,7 +4484,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>142</v>
       </c>
@@ -4163,7 +4540,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>148</v>
       </c>
@@ -4219,7 +4596,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>158</v>
       </c>
@@ -4275,7 +4652,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>164</v>
       </c>
@@ -4331,7 +4708,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>169</v>
       </c>
@@ -4387,7 +4764,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>178</v>
       </c>
@@ -4443,7 +4820,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>185</v>
       </c>
@@ -4499,7 +4876,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>190</v>
       </c>
@@ -4555,7 +4932,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>198</v>
       </c>
@@ -4611,7 +4988,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>206</v>
       </c>
@@ -4667,7 +5044,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>213</v>
       </c>
@@ -4723,7 +5100,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>218</v>
       </c>
@@ -4779,7 +5156,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>223</v>
       </c>
@@ -4835,7 +5212,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>229</v>
       </c>
@@ -4891,7 +5268,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>236</v>
       </c>
@@ -4947,7 +5324,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>239</v>
       </c>
@@ -5003,7 +5380,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="1:18">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>245</v>
       </c>
@@ -5059,7 +5436,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="34" spans="1:18">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>250</v>
       </c>
@@ -5115,7 +5492,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:18">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>258</v>
       </c>
@@ -5171,7 +5548,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:18">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>263</v>
       </c>
@@ -5227,7 +5604,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="37" spans="1:18">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>267</v>
       </c>
@@ -5283,7 +5660,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:18">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>273</v>
       </c>
@@ -5339,7 +5716,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:18">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>279</v>
       </c>
@@ -5395,7 +5772,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:18">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>285</v>
       </c>
@@ -5451,7 +5828,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="41" spans="1:18">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>291</v>
       </c>
@@ -5507,7 +5884,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:18">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>299</v>
       </c>
@@ -5563,7 +5940,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:18">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>307</v>
       </c>
@@ -5619,7 +5996,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="44" spans="1:18">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>314</v>
       </c>
@@ -5675,7 +6052,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="45" spans="1:18">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>284</v>
       </c>
@@ -5731,7 +6108,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:18">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>323</v>
       </c>
@@ -5787,7 +6164,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="47" spans="1:18">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>329</v>
       </c>
@@ -5843,7 +6220,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:18">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>337</v>
       </c>
@@ -5899,7 +6276,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:18">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>340</v>
       </c>
@@ -5955,7 +6332,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="50" spans="1:18">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>344</v>
       </c>
@@ -6011,7 +6388,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:18">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>349</v>
       </c>
@@ -6067,7 +6444,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="1:18">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>355</v>
       </c>
@@ -6123,7 +6500,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="53" spans="1:18">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>362</v>
       </c>
@@ -6179,7 +6556,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="1:18">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>370</v>
       </c>
@@ -6235,7 +6612,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="1:18">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>376</v>
       </c>
@@ -6291,7 +6668,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="56" spans="1:18">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>381</v>
       </c>
@@ -6347,7 +6724,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:18">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>385</v>
       </c>
@@ -6403,7 +6780,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:18">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>391</v>
       </c>
@@ -6459,7 +6836,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="59" spans="1:18">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>397</v>
       </c>
@@ -6515,7 +6892,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:18">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>404</v>
       </c>
@@ -6571,7 +6948,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="61" spans="1:18">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>410</v>
       </c>
@@ -6627,7 +7004,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:18">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>413</v>
       </c>
@@ -6683,7 +7060,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="63" spans="1:18">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>419</v>
       </c>
@@ -6739,7 +7116,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="64" spans="1:18">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>425</v>
       </c>
@@ -6795,7 +7172,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="65" spans="1:18">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>431</v>
       </c>
@@ -6851,7 +7228,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="66" spans="1:18">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>436</v>
       </c>
@@ -6907,7 +7284,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:18">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>443</v>
       </c>
@@ -6963,7 +7340,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="68" spans="1:18">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>447</v>
       </c>
@@ -7019,7 +7396,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="69" spans="1:18">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>455</v>
       </c>
@@ -7075,7 +7452,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="70" spans="1:18">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>460</v>
       </c>
@@ -7131,7 +7508,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="71" spans="1:18">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>465</v>
       </c>
@@ -7187,7 +7564,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="72" spans="1:18">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>469</v>
       </c>
@@ -7243,7 +7620,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="73" spans="1:18">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>352</v>
       </c>
@@ -7299,7 +7676,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="74" spans="1:18">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>476</v>
       </c>
@@ -7355,7 +7732,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="75" spans="1:18">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>483</v>
       </c>
@@ -7411,7 +7788,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="76" spans="1:18">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>359</v>
       </c>
@@ -7467,7 +7844,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="77" spans="1:18">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>369</v>
       </c>
@@ -7523,7 +7900,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="78" spans="1:18">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>498</v>
       </c>
@@ -7579,7 +7956,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="79" spans="1:18">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>503</v>
       </c>
@@ -7635,7 +8012,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="80" spans="1:18">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>509</v>
       </c>
@@ -7691,7 +8068,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="81" spans="1:18">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>513</v>
       </c>
@@ -7747,7 +8124,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="82" spans="1:18">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>518</v>
       </c>
@@ -7803,7 +8180,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:18">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>524</v>
       </c>
@@ -7859,7 +8236,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" spans="1:18">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>529</v>
       </c>
@@ -7915,7 +8292,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="85" spans="1:18">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>534</v>
       </c>
@@ -7971,7 +8348,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="86" spans="1:18">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>540</v>
       </c>
@@ -8027,7 +8404,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="87" spans="1:18">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>545</v>
       </c>
@@ -8083,7 +8460,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="88" spans="1:18">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>551</v>
       </c>
@@ -8139,7 +8516,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="89" spans="1:18">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>554</v>
       </c>
@@ -8195,7 +8572,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:18">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>559</v>
       </c>
@@ -8251,7 +8628,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="1:18">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>563</v>
       </c>
@@ -8307,7 +8684,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="92" spans="1:18">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>569</v>
       </c>
@@ -8363,7 +8740,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="93" spans="1:18">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>575</v>
       </c>
@@ -8419,7 +8796,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:18">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>580</v>
       </c>
@@ -8475,7 +8852,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="95" spans="1:18">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>587</v>
       </c>
@@ -8531,7 +8908,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="96" spans="1:18">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>592</v>
       </c>
@@ -8587,7 +8964,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="97" spans="1:18">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>596</v>
       </c>
@@ -8643,7 +9020,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="98" spans="1:18">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>602</v>
       </c>
@@ -8699,7 +9076,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="99" spans="1:18">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>607</v>
       </c>
@@ -8755,7 +9132,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="100" spans="1:18">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>614</v>
       </c>
@@ -8811,7 +9188,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="101" spans="1:18">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>621</v>
       </c>
@@ -8867,7 +9244,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="102" spans="1:18">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>627</v>
       </c>
@@ -8923,7 +9300,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="103" spans="1:18">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>632</v>
       </c>
@@ -8979,7 +9356,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="104" spans="1:18">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>636</v>
       </c>
@@ -9035,7 +9412,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="105" spans="1:18">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>641</v>
       </c>
@@ -9091,7 +9468,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="106" spans="1:18">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>647</v>
       </c>
@@ -9147,7 +9524,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="107" spans="1:18">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>652</v>
       </c>
@@ -9203,7 +9580,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="108" spans="1:18">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>656</v>
       </c>
@@ -9259,7 +9636,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="109" spans="1:18">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>661</v>
       </c>
@@ -9325,412 +9702,440 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB0C43B-B9E0-48B6-920B-AE77AC118324}">
-  <dimension ref="A1:N139"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:O139"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>665</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
         <v>666</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>667</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>668</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>669</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>670</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>671</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>672</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>673</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>674</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>675</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>677</v>
-      </c>
-      <c r="B2" s="19">
-        <v>33289</v>
-      </c>
-      <c r="C2" t="s">
-        <v>329</v>
+        <v>719</v>
+      </c>
+      <c r="B2" t="s">
+        <v>866</v>
+      </c>
+      <c r="C2" s="19">
+        <v>25385</v>
       </c>
       <c r="D2" t="s">
-        <v>336</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="2">
-        <v>90</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="H2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="2">
+        <v>250</v>
+      </c>
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>1060</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>678</v>
       </c>
-      <c r="M2">
-        <f>COUNTIF(Tabela2[Mapa],J2)</f>
+      <c r="N2">
+        <f>COUNTIF(Tabela2[Mapa],K2)</f>
         <v>8</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>679</v>
-      </c>
-      <c r="B3" s="19">
-        <v>42736</v>
-      </c>
-      <c r="C3" t="s">
-        <v>329</v>
+        <v>734</v>
+      </c>
+      <c r="B3" t="s">
+        <v>867</v>
+      </c>
+      <c r="C3" s="19">
+        <v>24812</v>
       </c>
       <c r="D3" t="s">
-        <v>336</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="3">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="I3" s="3">
+        <v>250</v>
+      </c>
+      <c r="K3" t="s">
         <v>38</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>935</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>678</v>
       </c>
-      <c r="M3">
-        <f>COUNTIF(Tabela2[Mapa],J3)</f>
+      <c r="N3">
+        <f>COUNTIF(Tabela2[Mapa],K3)</f>
         <v>8</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>680</v>
-      </c>
-      <c r="B4" s="19">
-        <v>43831</v>
-      </c>
-      <c r="C4" t="s">
-        <v>349</v>
+        <v>690</v>
+      </c>
+      <c r="B4" t="s">
+        <v>848</v>
+      </c>
+      <c r="C4" s="19">
+        <v>30997</v>
       </c>
       <c r="D4" t="s">
-        <v>352</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="3">
-        <v>30</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="3">
+        <v>200</v>
+      </c>
+      <c r="K4" t="s">
         <v>89</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>530</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>678</v>
       </c>
-      <c r="M4">
-        <f>COUNTIF(Tabela2[Mapa],J4)</f>
+      <c r="N4">
+        <f>COUNTIF(Tabela2[Mapa],K4)</f>
         <v>5</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>681</v>
-      </c>
-      <c r="B5" s="19">
-        <v>25934</v>
-      </c>
-      <c r="C5" t="s">
-        <v>551</v>
+        <v>727</v>
+      </c>
+      <c r="B5" t="s">
+        <v>868</v>
+      </c>
+      <c r="C5" s="19">
+        <v>28281</v>
       </c>
       <c r="D5" t="s">
-        <v>442</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="3">
+        <v>200</v>
+      </c>
+      <c r="K5" t="s">
+        <v>210</v>
+      </c>
+      <c r="L5">
+        <v>490</v>
+      </c>
+      <c r="M5" t="s">
+        <v>678</v>
+      </c>
+      <c r="N5">
+        <f>COUNTIF(Tabela2[Mapa],K5)</f>
+        <v>5</v>
+      </c>
+      <c r="O5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>735</v>
+      </c>
+      <c r="B6" t="s">
+        <v>831</v>
+      </c>
+      <c r="C6" s="19">
+        <v>28239</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
         <v>26</v>
       </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="3">
-        <v>20</v>
-      </c>
-      <c r="J5" t="s">
-        <v>210</v>
-      </c>
-      <c r="K5">
-        <v>490</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="3">
+        <v>200</v>
+      </c>
+      <c r="K6" t="s">
+        <v>178</v>
+      </c>
+      <c r="L6">
+        <v>430</v>
+      </c>
+      <c r="M6" t="s">
         <v>678</v>
       </c>
-      <c r="M5">
-        <f>COUNTIF(Tabela2[Mapa],J5)</f>
+      <c r="N6">
+        <f>COUNTIF(Tabela2[Mapa],K6)</f>
+        <v>7</v>
+      </c>
+      <c r="O6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>765</v>
+      </c>
+      <c r="B7" t="s">
+        <v>870</v>
+      </c>
+      <c r="C7" s="19">
+        <v>30327</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="3">
+        <v>200</v>
+      </c>
+      <c r="K7" t="s">
+        <v>173</v>
+      </c>
+      <c r="L7">
+        <v>390</v>
+      </c>
+      <c r="M7" t="s">
+        <v>684</v>
+      </c>
+      <c r="N7">
+        <f>COUNTIF(Tabela2[Mapa],K7)</f>
+        <v>6</v>
+      </c>
+      <c r="O7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>787</v>
+      </c>
+      <c r="B8" t="s">
+        <v>875</v>
+      </c>
+      <c r="C8" s="19">
+        <v>26497</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="3">
+        <v>200</v>
+      </c>
+      <c r="K8" t="s">
+        <v>132</v>
+      </c>
+      <c r="L8">
+        <v>375</v>
+      </c>
+      <c r="M8" t="s">
+        <v>684</v>
+      </c>
+      <c r="N8">
+        <f>COUNTIF(Tabela2[Mapa],K8)</f>
         <v>5</v>
       </c>
-      <c r="N5">
+      <c r="O8">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>682</v>
-      </c>
-      <c r="B6" s="19">
-        <v>37510</v>
-      </c>
-      <c r="C6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" t="s">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>795</v>
+      </c>
+      <c r="B9" t="s">
+        <v>871</v>
+      </c>
+      <c r="C9" s="19">
+        <v>25618</v>
+      </c>
+      <c r="D9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" t="s">
         <v>27</v>
       </c>
-      <c r="G6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="3">
-        <v>20</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="I9" s="3">
+        <v>200</v>
+      </c>
+      <c r="K9" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9">
+        <v>325</v>
+      </c>
+      <c r="M9" t="s">
+        <v>684</v>
+      </c>
+      <c r="N9">
+        <f>COUNTIF(Tabela2[Mapa],K9)</f>
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>713</v>
+      </c>
+      <c r="B10" t="s">
+        <v>850</v>
+      </c>
+      <c r="C10" s="19">
+        <v>30238</v>
+      </c>
+      <c r="D10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E10" t="s">
         <v>178</v>
-      </c>
-      <c r="K6">
-        <v>430</v>
-      </c>
-      <c r="L6" t="s">
-        <v>678</v>
-      </c>
-      <c r="M6">
-        <f>COUNTIF(Tabela2[Mapa],J6)</f>
-        <v>7</v>
-      </c>
-      <c r="N6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>683</v>
-      </c>
-      <c r="B7" s="19">
-        <v>33340</v>
-      </c>
-      <c r="C7" t="s">
-        <v>337</v>
-      </c>
-      <c r="D7" t="s">
-        <v>336</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="3">
-        <v>90</v>
-      </c>
-      <c r="J7" t="s">
-        <v>173</v>
-      </c>
-      <c r="K7">
-        <v>390</v>
-      </c>
-      <c r="L7" t="s">
-        <v>684</v>
-      </c>
-      <c r="M7">
-        <f>COUNTIF(Tabela2[Mapa],J7)</f>
-        <v>6</v>
-      </c>
-      <c r="N7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>685</v>
-      </c>
-      <c r="B8" s="19">
-        <v>37157</v>
-      </c>
-      <c r="C8" t="s">
-        <v>559</v>
-      </c>
-      <c r="D8" t="s">
-        <v>442</v>
-      </c>
-      <c r="E8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="3">
-        <v>20</v>
-      </c>
-      <c r="J8" t="s">
-        <v>132</v>
-      </c>
-      <c r="K8">
-        <v>375</v>
-      </c>
-      <c r="L8" t="s">
-        <v>684</v>
-      </c>
-      <c r="M8">
-        <f>COUNTIF(Tabela2[Mapa],J8)</f>
-        <v>5</v>
-      </c>
-      <c r="N8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>686</v>
-      </c>
-      <c r="B9" s="19">
-        <v>36754</v>
-      </c>
-      <c r="C9" t="s">
-        <v>431</v>
-      </c>
-      <c r="D9" t="s">
-        <v>257</v>
-      </c>
-      <c r="E9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="3">
-        <v>40</v>
-      </c>
-      <c r="J9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K9">
-        <v>325</v>
-      </c>
-      <c r="L9" t="s">
-        <v>684</v>
-      </c>
-      <c r="M9">
-        <f>COUNTIF(Tabela2[Mapa],J9)</f>
-        <v>5</v>
-      </c>
-      <c r="N9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>687</v>
-      </c>
-      <c r="B10" s="19">
-        <v>44562</v>
-      </c>
-      <c r="C10" t="s">
-        <v>273</v>
-      </c>
-      <c r="D10" t="s">
-        <v>278</v>
-      </c>
-      <c r="E10" t="s">
-        <v>42</v>
       </c>
       <c r="F10" t="s">
         <v>27</v>
@@ -9738,713 +10143,764 @@
       <c r="G10" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="3">
-        <v>20</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="H10" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="3">
+        <v>150</v>
+      </c>
+      <c r="K10" t="s">
         <v>108</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>300</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>684</v>
       </c>
-      <c r="M10">
-        <f>COUNTIF(Tabela2[Mapa],J10)</f>
+      <c r="N10">
+        <f>COUNTIF(Tabela2[Mapa],K10)</f>
         <v>5</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>688</v>
-      </c>
-      <c r="B11" s="19">
-        <v>28422</v>
-      </c>
-      <c r="C11" t="s">
-        <v>128</v>
+        <v>738</v>
+      </c>
+      <c r="B11" t="s">
+        <v>876</v>
+      </c>
+      <c r="C11" s="19">
+        <v>33286</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="E11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="3">
+        <v>150</v>
+      </c>
+      <c r="K11" t="s">
+        <v>202</v>
+      </c>
+      <c r="L11">
+        <v>290</v>
+      </c>
+      <c r="M11" t="s">
+        <v>684</v>
+      </c>
+      <c r="N11">
+        <f>COUNTIF(Tabela2[Mapa],K11)</f>
+        <v>4</v>
+      </c>
+      <c r="O11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>780</v>
+      </c>
+      <c r="B12" t="s">
+        <v>877</v>
+      </c>
+      <c r="C12" s="19">
+        <v>33719</v>
+      </c>
+      <c r="D12" t="s">
+        <v>284</v>
+      </c>
+      <c r="E12" t="s">
+        <v>210</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="3">
+        <v>150</v>
+      </c>
+      <c r="K12" t="s">
+        <v>306</v>
+      </c>
+      <c r="L12">
+        <v>260</v>
+      </c>
+      <c r="M12" t="s">
+        <v>684</v>
+      </c>
+      <c r="N12">
+        <f>COUNTIF(Tabela2[Mapa],K12)</f>
+        <v>5</v>
+      </c>
+      <c r="O12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>791</v>
+      </c>
+      <c r="B13" t="s">
+        <v>878</v>
+      </c>
+      <c r="C13" s="19">
+        <v>34990</v>
+      </c>
+      <c r="D13" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F13" t="s">
+        <v>117</v>
+      </c>
+      <c r="G13" t="s">
+        <v>117</v>
+      </c>
+      <c r="H13" t="s">
         <v>26</v>
       </c>
-      <c r="F11" t="s">
+      <c r="I13" s="3">
+        <v>150</v>
+      </c>
+      <c r="K13" t="s">
+        <v>197</v>
+      </c>
+      <c r="L13">
+        <v>260</v>
+      </c>
+      <c r="M13" t="s">
+        <v>684</v>
+      </c>
+      <c r="N13">
+        <f>COUNTIF(Tabela2[Mapa],K13)</f>
+        <v>5</v>
+      </c>
+      <c r="O13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>696</v>
+      </c>
+      <c r="B14" t="s">
+        <v>849</v>
+      </c>
+      <c r="C14" s="19">
+        <v>28491</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" t="s">
+        <v>694</v>
+      </c>
+      <c r="H14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="3">
+        <v>140</v>
+      </c>
+      <c r="K14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L14">
+        <v>245</v>
+      </c>
+      <c r="M14" t="s">
+        <v>684</v>
+      </c>
+      <c r="N14">
+        <f>COUNTIF(Tabela2[Mapa],K14)</f>
+        <v>5</v>
+      </c>
+      <c r="O14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>744</v>
+      </c>
+      <c r="B15" t="s">
+        <v>872</v>
+      </c>
+      <c r="C15" s="19">
+        <v>28421</v>
+      </c>
+      <c r="D15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" t="s">
         <v>27</v>
       </c>
-      <c r="G11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="3">
-        <v>120</v>
-      </c>
-      <c r="J11" t="s">
-        <v>202</v>
-      </c>
-      <c r="K11">
-        <v>290</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="H15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="3">
+        <v>140</v>
+      </c>
+      <c r="K15" t="s">
+        <v>257</v>
+      </c>
+      <c r="L15">
+        <v>225</v>
+      </c>
+      <c r="M15" t="s">
         <v>684</v>
       </c>
-      <c r="M11">
-        <f>COUNTIF(Tabela2[Mapa],J11)</f>
+      <c r="N15">
+        <f>COUNTIF(Tabela2[Mapa],K15)</f>
+        <v>5</v>
+      </c>
+      <c r="O15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>750</v>
+      </c>
+      <c r="B16" t="s">
+        <v>879</v>
+      </c>
+      <c r="C16" s="19">
+        <v>25488</v>
+      </c>
+      <c r="D16" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="3">
+        <v>140</v>
+      </c>
+      <c r="K16" t="s">
+        <v>369</v>
+      </c>
+      <c r="L16">
+        <v>220</v>
+      </c>
+      <c r="M16" t="s">
+        <v>684</v>
+      </c>
+      <c r="N16">
+        <f>COUNTIF(Tabela2[Mapa],K16)</f>
         <v>4</v>
       </c>
-      <c r="N11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" t="s">
-        <v>689</v>
-      </c>
-      <c r="B12" s="19">
-        <v>33865</v>
-      </c>
-      <c r="C12" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" t="s">
-        <v>132</v>
-      </c>
-      <c r="E12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="3">
-        <v>20</v>
-      </c>
-      <c r="J12" t="s">
-        <v>306</v>
-      </c>
-      <c r="K12">
-        <v>260</v>
-      </c>
-      <c r="L12" t="s">
-        <v>684</v>
-      </c>
-      <c r="M12">
-        <f>COUNTIF(Tabela2[Mapa],J12)</f>
-        <v>5</v>
-      </c>
-      <c r="N12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>690</v>
-      </c>
-      <c r="B13" s="19">
-        <v>30997</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="3">
-        <v>200</v>
-      </c>
-      <c r="J13" t="s">
-        <v>197</v>
-      </c>
-      <c r="K13">
-        <v>260</v>
-      </c>
-      <c r="L13" t="s">
-        <v>684</v>
-      </c>
-      <c r="M13">
-        <f>COUNTIF(Tabela2[Mapa],J13)</f>
-        <v>5</v>
-      </c>
-      <c r="N13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
-        <v>691</v>
-      </c>
-      <c r="B14" s="19">
-        <v>32899</v>
-      </c>
-      <c r="C14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" s="3">
-        <v>50</v>
-      </c>
-      <c r="J14" t="s">
-        <v>336</v>
-      </c>
-      <c r="K14">
-        <v>245</v>
-      </c>
-      <c r="L14" t="s">
-        <v>684</v>
-      </c>
-      <c r="M14">
-        <f>COUNTIF(Tabela2[Mapa],J14)</f>
-        <v>5</v>
-      </c>
-      <c r="N14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
-        <v>692</v>
-      </c>
-      <c r="B15" s="19">
-        <v>40011</v>
-      </c>
-      <c r="C15" t="s">
-        <v>213</v>
-      </c>
-      <c r="D15" t="s">
-        <v>202</v>
-      </c>
-      <c r="E15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="3">
-        <v>40</v>
-      </c>
-      <c r="J15" t="s">
-        <v>257</v>
-      </c>
-      <c r="K15">
-        <v>225</v>
-      </c>
-      <c r="L15" t="s">
-        <v>684</v>
-      </c>
-      <c r="M15">
-        <f>COUNTIF(Tabela2[Mapa],J15)</f>
-        <v>5</v>
-      </c>
-      <c r="N15">
+      <c r="O16">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
-      <c r="A16" t="s">
-        <v>693</v>
-      </c>
-      <c r="B16" s="19">
-        <v>34751</v>
-      </c>
-      <c r="C16" t="s">
-        <v>245</v>
-      </c>
-      <c r="D16" t="s">
-        <v>249</v>
-      </c>
-      <c r="E16" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" t="s">
-        <v>694</v>
-      </c>
-      <c r="G16" t="s">
-        <v>695</v>
-      </c>
-      <c r="H16" s="3">
-        <v>80</v>
-      </c>
-      <c r="J16" t="s">
-        <v>369</v>
-      </c>
-      <c r="K16">
-        <v>220</v>
-      </c>
-      <c r="L16" t="s">
-        <v>684</v>
-      </c>
-      <c r="M16">
-        <f>COUNTIF(Tabela2[Mapa],J16)</f>
-        <v>4</v>
-      </c>
-      <c r="N16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>696</v>
-      </c>
-      <c r="B17" s="19">
-        <v>28491</v>
-      </c>
-      <c r="C17" t="s">
-        <v>60</v>
+        <v>768</v>
+      </c>
+      <c r="B17" t="s">
+        <v>880</v>
+      </c>
+      <c r="C17" s="19">
+        <v>32675</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>323</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>173</v>
       </c>
       <c r="F17" t="s">
         <v>694</v>
       </c>
       <c r="G17" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" s="3">
+        <v>140</v>
+      </c>
+      <c r="K17" t="s">
+        <v>249</v>
+      </c>
+      <c r="L17">
+        <v>180</v>
+      </c>
+      <c r="M17" t="s">
+        <v>697</v>
+      </c>
+      <c r="N17">
+        <f>COUNTIF(Tabela2[Mapa],K17)</f>
+        <v>3</v>
+      </c>
+      <c r="O17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>774</v>
+      </c>
+      <c r="B18" t="s">
+        <v>881</v>
+      </c>
+      <c r="C18" s="19">
+        <v>32598</v>
+      </c>
+      <c r="D18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E18" t="s">
+        <v>173</v>
+      </c>
+      <c r="F18" t="s">
+        <v>775</v>
+      </c>
+      <c r="G18" t="s">
+        <v>775</v>
+      </c>
+      <c r="H18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" s="3">
+        <v>140</v>
+      </c>
+      <c r="K18" t="s">
+        <v>127</v>
+      </c>
+      <c r="L18">
+        <v>180</v>
+      </c>
+      <c r="M18" t="s">
+        <v>697</v>
+      </c>
+      <c r="N18">
+        <f>COUNTIF(Tabela2[Mapa],K18)</f>
+        <v>4</v>
+      </c>
+      <c r="O18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>722</v>
+      </c>
+      <c r="B19" t="s">
+        <v>882</v>
+      </c>
+      <c r="C19" s="19">
+        <v>28400</v>
+      </c>
+      <c r="D19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E19" t="s">
+        <v>132</v>
+      </c>
+      <c r="F19" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" t="s">
+        <v>41</v>
+      </c>
+      <c r="H19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="3">
+        <v>130</v>
+      </c>
+      <c r="K19" t="s">
+        <v>409</v>
+      </c>
+      <c r="L19">
+        <v>180</v>
+      </c>
+      <c r="M19" t="s">
+        <v>697</v>
+      </c>
+      <c r="N19">
+        <f>COUNTIF(Tabela2[Mapa],K19)</f>
+        <v>3</v>
+      </c>
+      <c r="O19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>688</v>
+      </c>
+      <c r="B20" t="s">
+        <v>847</v>
+      </c>
+      <c r="C20" s="19">
+        <v>28422</v>
+      </c>
+      <c r="D20" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="3">
-        <v>140</v>
-      </c>
-      <c r="J17" t="s">
-        <v>249</v>
-      </c>
-      <c r="K17">
-        <v>180</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="G20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="3">
+        <v>120</v>
+      </c>
+      <c r="K20" t="s">
+        <v>119</v>
+      </c>
+      <c r="L20">
+        <v>160</v>
+      </c>
+      <c r="M20" t="s">
         <v>697</v>
       </c>
-      <c r="M17">
-        <f>COUNTIF(Tabela2[Mapa],J17)</f>
-        <v>3</v>
-      </c>
-      <c r="N17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>698</v>
-      </c>
-      <c r="B18" s="19">
-        <v>32607</v>
-      </c>
-      <c r="C18" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" t="s">
-        <v>695</v>
-      </c>
-      <c r="H18" s="3">
-        <v>45</v>
-      </c>
-      <c r="J18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K18">
-        <v>180</v>
-      </c>
-      <c r="L18" t="s">
-        <v>697</v>
-      </c>
-      <c r="M18">
-        <f>COUNTIF(Tabela2[Mapa],J18)</f>
-        <v>4</v>
-      </c>
-      <c r="N18">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" t="s">
-        <v>699</v>
-      </c>
-      <c r="B19" s="19">
-        <v>37306</v>
-      </c>
-      <c r="C19" t="s">
-        <v>518</v>
-      </c>
-      <c r="D19" t="s">
-        <v>442</v>
-      </c>
-      <c r="E19" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="3">
-        <v>30</v>
-      </c>
-      <c r="J19" t="s">
-        <v>409</v>
-      </c>
-      <c r="K19">
-        <v>180</v>
-      </c>
-      <c r="L19" t="s">
-        <v>697</v>
-      </c>
-      <c r="M19">
-        <f>COUNTIF(Tabela2[Mapa],J19)</f>
-        <v>3</v>
-      </c>
-      <c r="N19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" t="s">
-        <v>700</v>
-      </c>
-      <c r="B20" s="19">
-        <v>38564</v>
-      </c>
-      <c r="C20" t="s">
-        <v>534</v>
-      </c>
-      <c r="D20" t="s">
-        <v>336</v>
-      </c>
-      <c r="E20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="3">
-        <v>20</v>
-      </c>
-      <c r="J20" t="s">
-        <v>119</v>
-      </c>
-      <c r="K20">
-        <v>160</v>
-      </c>
-      <c r="L20" t="s">
-        <v>697</v>
-      </c>
-      <c r="M20">
-        <f>COUNTIF(Tabela2[Mapa],J20)</f>
+      <c r="N20">
+        <f>COUNTIF(Tabela2[Mapa],K20)</f>
         <v>7</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>701</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" t="s">
+        <v>856</v>
+      </c>
+      <c r="C21" s="19">
         <v>37063</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>78</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>23</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>27</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>117</v>
       </c>
-      <c r="G21" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="H21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="3">
         <v>120</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>156</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>150</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>697</v>
       </c>
-      <c r="M21">
-        <f>COUNTIF(Tabela2[Mapa],J21)</f>
+      <c r="N21">
+        <f>COUNTIF(Tabela2[Mapa],K21)</f>
         <v>3</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>702</v>
-      </c>
-      <c r="B22" s="19">
-        <v>25455</v>
-      </c>
-      <c r="C22" t="s">
-        <v>78</v>
+        <v>736</v>
+      </c>
+      <c r="B22" t="s">
+        <v>883</v>
+      </c>
+      <c r="C22" s="19">
+        <v>25914</v>
       </c>
       <c r="D22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" t="s">
         <v>23</v>
       </c>
-      <c r="E22" t="s">
-        <v>42</v>
-      </c>
       <c r="F22" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" s="3">
+        <v>120</v>
+      </c>
+      <c r="K22" t="s">
+        <v>98</v>
+      </c>
+      <c r="L22">
+        <v>150</v>
+      </c>
+      <c r="M22" t="s">
+        <v>697</v>
+      </c>
+      <c r="N22">
+        <f>COUNTIF(Tabela2[Mapa],K22)</f>
+        <v>3</v>
+      </c>
+      <c r="O22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>741</v>
+      </c>
+      <c r="B23" t="s">
+        <v>873</v>
+      </c>
+      <c r="C23" s="19">
+        <v>35573</v>
+      </c>
+      <c r="D23" t="s">
+        <v>198</v>
+      </c>
+      <c r="E23" t="s">
+        <v>202</v>
+      </c>
+      <c r="F23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" s="3">
+        <v>120</v>
+      </c>
+      <c r="K23" t="s">
+        <v>442</v>
+      </c>
+      <c r="L23">
+        <v>130</v>
+      </c>
+      <c r="M23" t="s">
+        <v>697</v>
+      </c>
+      <c r="N23">
+        <f>COUNTIF(Tabela2[Mapa],K23)</f>
+        <v>6</v>
+      </c>
+      <c r="O23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>783</v>
+      </c>
+      <c r="B24" t="s">
+        <v>878</v>
+      </c>
+      <c r="C24" s="19">
+        <v>25472</v>
+      </c>
+      <c r="D24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" t="s">
         <v>27</v>
       </c>
-      <c r="G22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H22" s="3">
-        <v>80</v>
-      </c>
-      <c r="J22" t="s">
-        <v>98</v>
-      </c>
-      <c r="K22">
-        <v>150</v>
-      </c>
-      <c r="L22" t="s">
+      <c r="I24" s="3">
+        <v>120</v>
+      </c>
+      <c r="K24" t="s">
+        <v>705</v>
+      </c>
+      <c r="L24">
+        <v>130</v>
+      </c>
+      <c r="M24" t="s">
         <v>697</v>
       </c>
-      <c r="M22">
-        <f>COUNTIF(Tabela2[Mapa],J22)</f>
-        <v>3</v>
-      </c>
-      <c r="N22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" t="s">
-        <v>703</v>
-      </c>
-      <c r="B23" s="19">
-        <v>39675</v>
-      </c>
-      <c r="C23" t="s">
-        <v>299</v>
-      </c>
-      <c r="D23" t="s">
-        <v>306</v>
-      </c>
-      <c r="E23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23" s="3">
-        <v>60</v>
-      </c>
-      <c r="J23" t="s">
-        <v>442</v>
-      </c>
-      <c r="K23">
-        <v>130</v>
-      </c>
-      <c r="L23" t="s">
-        <v>697</v>
-      </c>
-      <c r="M23">
-        <f>COUNTIF(Tabela2[Mapa],J23)</f>
-        <v>6</v>
-      </c>
-      <c r="N23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" t="s">
-        <v>704</v>
-      </c>
-      <c r="B24" s="19">
-        <v>35512</v>
-      </c>
-      <c r="C24" t="s">
-        <v>299</v>
-      </c>
-      <c r="D24" t="s">
-        <v>306</v>
-      </c>
-      <c r="E24" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" t="s">
-        <v>42</v>
-      </c>
-      <c r="G24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H24" s="3">
-        <v>60</v>
-      </c>
-      <c r="J24" t="s">
-        <v>705</v>
-      </c>
-      <c r="K24">
-        <v>130</v>
-      </c>
-      <c r="L24" t="s">
-        <v>697</v>
-      </c>
-      <c r="M24">
-        <f>COUNTIF(Tabela2[Mapa],J24)</f>
+      <c r="N24">
+        <f>COUNTIF(Tabela2[Mapa],K24)</f>
         <v>5</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>706</v>
-      </c>
-      <c r="B25" s="19">
-        <v>33639</v>
-      </c>
-      <c r="C25" t="s">
-        <v>279</v>
+        <v>761</v>
+      </c>
+      <c r="B25" t="s">
+        <v>884</v>
+      </c>
+      <c r="C25" s="19">
+        <v>30717</v>
       </c>
       <c r="D25" t="s">
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H25" s="3">
-        <v>40</v>
-      </c>
-      <c r="J25" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" s="3">
+        <v>100</v>
+      </c>
+      <c r="K25" t="s">
         <v>352</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>120</v>
       </c>
-      <c r="L25" t="s">
+      <c r="M25" t="s">
         <v>697</v>
       </c>
-      <c r="M25">
-        <f>COUNTIF(Tabela2[Mapa],J25)</f>
+      <c r="N25">
+        <f>COUNTIF(Tabela2[Mapa],K25)</f>
         <v>4</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>707</v>
-      </c>
-      <c r="B26" s="19">
-        <v>32489</v>
-      </c>
-      <c r="C26" t="s">
+        <v>797</v>
+      </c>
+      <c r="B26" t="s">
+        <v>885</v>
+      </c>
+      <c r="C26" s="19">
+        <v>34502</v>
+      </c>
+      <c r="D26" t="s">
+        <v>263</v>
+      </c>
+      <c r="E26" t="s">
+        <v>202</v>
+      </c>
+      <c r="F26" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26" s="3">
+        <v>100</v>
+      </c>
+      <c r="K26" t="s">
+        <v>244</v>
+      </c>
+      <c r="L26">
         <v>120</v>
       </c>
-      <c r="D26" t="s">
-        <v>127</v>
-      </c>
-      <c r="E26" t="s">
-        <v>708</v>
-      </c>
-      <c r="F26" t="s">
-        <v>42</v>
-      </c>
-      <c r="G26" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" s="3">
-        <v>20</v>
-      </c>
-      <c r="J26" t="s">
-        <v>244</v>
-      </c>
-      <c r="K26">
-        <v>120</v>
-      </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>697</v>
       </c>
-      <c r="M26">
-        <f>COUNTIF(Tabela2[Mapa],J26)</f>
+      <c r="N26">
+        <f>COUNTIF(Tabela2[Mapa],K26)</f>
         <v>3</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>709</v>
-      </c>
-      <c r="B27" s="19">
-        <v>35898</v>
-      </c>
-      <c r="C27" t="s">
-        <v>355</v>
+        <v>798</v>
+      </c>
+      <c r="B27" t="s">
+        <v>886</v>
+      </c>
+      <c r="C27" s="19">
+        <v>35723</v>
       </c>
       <c r="D27" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F27" t="s">
         <v>42</v>
@@ -10452,41 +10908,44 @@
       <c r="G27" t="s">
         <v>27</v>
       </c>
-      <c r="H27" s="3">
-        <v>60</v>
-      </c>
-      <c r="J27" t="s">
+      <c r="H27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="3">
+        <v>100</v>
+      </c>
+      <c r="K27" t="s">
         <v>488</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>110</v>
       </c>
-      <c r="L27" t="s">
+      <c r="M27" t="s">
         <v>697</v>
       </c>
-      <c r="M27">
-        <f>COUNTIF(Tabela2[Mapa],J27)</f>
+      <c r="N27">
+        <f>COUNTIF(Tabela2[Mapa],K27)</f>
         <v>3</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>710</v>
-      </c>
-      <c r="B28" s="19">
-        <v>37031</v>
-      </c>
-      <c r="C28" t="s">
-        <v>455</v>
+        <v>677</v>
+      </c>
+      <c r="B28" t="s">
+        <v>829</v>
+      </c>
+      <c r="C28" s="19">
+        <v>33289</v>
       </c>
       <c r="D28" t="s">
-        <v>409</v>
+        <v>329</v>
       </c>
       <c r="E28" t="s">
-        <v>117</v>
+        <v>336</v>
       </c>
       <c r="F28" t="s">
         <v>42</v>
@@ -10494,453 +10953,498 @@
       <c r="G28" t="s">
         <v>42</v>
       </c>
-      <c r="H28" s="3">
-        <v>70</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="H28" t="s">
+        <v>27</v>
+      </c>
+      <c r="I28" s="3">
+        <v>90</v>
+      </c>
+      <c r="K28" t="s">
         <v>454</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>100</v>
       </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>697</v>
       </c>
-      <c r="M28">
-        <f>COUNTIF(Tabela2[Mapa],J28)</f>
+      <c r="N28">
+        <f>COUNTIF(Tabela2[Mapa],K28)</f>
         <v>3</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>711</v>
-      </c>
-      <c r="B29" s="19">
-        <v>37696</v>
-      </c>
-      <c r="C29" t="s">
-        <v>381</v>
+        <v>683</v>
+      </c>
+      <c r="B29" t="s">
+        <v>840</v>
+      </c>
+      <c r="C29" s="19">
+        <v>33340</v>
       </c>
       <c r="D29" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>336</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
       </c>
       <c r="G29" t="s">
+        <v>42</v>
+      </c>
+      <c r="H29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="3">
+        <v>90</v>
+      </c>
+      <c r="K29" t="s">
+        <v>228</v>
+      </c>
+      <c r="L29">
+        <v>70</v>
+      </c>
+      <c r="M29" t="s">
+        <v>697</v>
+      </c>
+      <c r="N29">
+        <f>COUNTIF(Tabela2[Mapa],K29)</f>
+        <v>3</v>
+      </c>
+      <c r="O29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>740</v>
+      </c>
+      <c r="B30" t="s">
+        <v>874</v>
+      </c>
+      <c r="C30" s="19">
+        <v>37683</v>
+      </c>
+      <c r="D30" t="s">
+        <v>404</v>
+      </c>
+      <c r="E30" t="s">
+        <v>409</v>
+      </c>
+      <c r="F30" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" t="s">
+        <v>41</v>
+      </c>
+      <c r="H30" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30" s="3">
+        <v>90</v>
+      </c>
+      <c r="K30" t="s">
+        <v>278</v>
+      </c>
+      <c r="L30">
+        <v>60</v>
+      </c>
+      <c r="M30" t="s">
+        <v>697</v>
+      </c>
+      <c r="N30">
+        <f>COUNTIF(Tabela2[Mapa],K30)</f>
+        <v>3</v>
+      </c>
+      <c r="O30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>693</v>
+      </c>
+      <c r="B31" t="s">
+        <v>837</v>
+      </c>
+      <c r="C31" s="19">
+        <v>34751</v>
+      </c>
+      <c r="D31" t="s">
+        <v>245</v>
+      </c>
+      <c r="E31" t="s">
+        <v>249</v>
+      </c>
+      <c r="F31" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" t="s">
+        <v>694</v>
+      </c>
+      <c r="H31" t="s">
+        <v>695</v>
+      </c>
+      <c r="I31" s="3">
+        <v>80</v>
+      </c>
+      <c r="K31" t="s">
+        <v>298</v>
+      </c>
+      <c r="L31">
+        <v>60</v>
+      </c>
+      <c r="M31" t="s">
+        <v>697</v>
+      </c>
+      <c r="N31">
+        <f>COUNTIF(Tabela2[Mapa],K31)</f>
+        <v>3</v>
+      </c>
+      <c r="O31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>702</v>
+      </c>
+      <c r="B32" t="s">
+        <v>857</v>
+      </c>
+      <c r="C32" s="19">
+        <v>25455</v>
+      </c>
+      <c r="D32" t="s">
+        <v>78</v>
+      </c>
+      <c r="E32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" t="s">
+        <v>42</v>
+      </c>
+      <c r="G32" t="s">
         <v>27</v>
       </c>
-      <c r="H29" s="3">
-        <v>60</v>
-      </c>
-      <c r="J29" t="s">
-        <v>228</v>
-      </c>
-      <c r="K29">
+      <c r="H32" t="s">
+        <v>27</v>
+      </c>
+      <c r="I32" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>724</v>
+      </c>
+      <c r="B33" t="s">
+        <v>887</v>
+      </c>
+      <c r="C33" s="19">
+        <v>34192</v>
+      </c>
+      <c r="D33" t="s">
+        <v>250</v>
+      </c>
+      <c r="E33" t="s">
+        <v>257</v>
+      </c>
+      <c r="F33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" t="s">
+        <v>42</v>
+      </c>
+      <c r="I33" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>730</v>
+      </c>
+      <c r="B34" t="s">
+        <v>853</v>
+      </c>
+      <c r="C34" s="19">
+        <v>33900</v>
+      </c>
+      <c r="D34" t="s">
+        <v>443</v>
+      </c>
+      <c r="E34" t="s">
+        <v>257</v>
+      </c>
+      <c r="F34" t="s">
+        <v>42</v>
+      </c>
+      <c r="G34" t="s">
+        <v>694</v>
+      </c>
+      <c r="H34" t="s">
+        <v>694</v>
+      </c>
+      <c r="I34" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>745</v>
+      </c>
+      <c r="B35" t="s">
+        <v>896</v>
+      </c>
+      <c r="C35" s="19">
+        <v>34241</v>
+      </c>
+      <c r="D35" t="s">
+        <v>307</v>
+      </c>
+      <c r="E35" t="s">
+        <v>127</v>
+      </c>
+      <c r="F35" t="s">
+        <v>42</v>
+      </c>
+      <c r="G35" t="s">
+        <v>41</v>
+      </c>
+      <c r="H35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I35" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>752</v>
+      </c>
+      <c r="B36" t="s">
+        <v>891</v>
+      </c>
+      <c r="C36" s="19">
+        <v>32993</v>
+      </c>
+      <c r="D36" t="s">
+        <v>190</v>
+      </c>
+      <c r="E36" t="s">
+        <v>197</v>
+      </c>
+      <c r="F36" t="s">
+        <v>42</v>
+      </c>
+      <c r="G36" t="s">
+        <v>41</v>
+      </c>
+      <c r="H36" t="s">
+        <v>41</v>
+      </c>
+      <c r="I36" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>745</v>
+      </c>
+      <c r="B37" t="s">
+        <v>889</v>
+      </c>
+      <c r="C37" s="19">
+        <v>34241</v>
+      </c>
+      <c r="D37" t="s">
+        <v>370</v>
+      </c>
+      <c r="E37" t="s">
+        <v>132</v>
+      </c>
+      <c r="F37" t="s">
+        <v>42</v>
+      </c>
+      <c r="G37" t="s">
+        <v>42</v>
+      </c>
+      <c r="H37" t="s">
+        <v>67</v>
+      </c>
+      <c r="I37" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>720</v>
+      </c>
+      <c r="B38" t="s">
+        <v>879</v>
+      </c>
+      <c r="C38" s="19">
+        <v>26153</v>
+      </c>
+      <c r="D38" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" t="s">
+        <v>42</v>
+      </c>
+      <c r="G38" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" t="s">
+        <v>708</v>
+      </c>
+      <c r="I38" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>710</v>
+      </c>
+      <c r="B39" t="s">
+        <v>842</v>
+      </c>
+      <c r="C39" s="19">
+        <v>37031</v>
+      </c>
+      <c r="D39" t="s">
+        <v>455</v>
+      </c>
+      <c r="E39" t="s">
+        <v>409</v>
+      </c>
+      <c r="F39" t="s">
+        <v>117</v>
+      </c>
+      <c r="G39" t="s">
+        <v>42</v>
+      </c>
+      <c r="H39" t="s">
+        <v>42</v>
+      </c>
+      <c r="I39" s="3">
         <v>70</v>
       </c>
-      <c r="L29" t="s">
-        <v>697</v>
-      </c>
-      <c r="M29">
-        <f>COUNTIF(Tabela2[Mapa],J29)</f>
-        <v>3</v>
-      </c>
-      <c r="N29">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" t="s">
-        <v>712</v>
-      </c>
-      <c r="B30" s="19">
-        <v>34398</v>
-      </c>
-      <c r="C30" t="s">
-        <v>385</v>
-      </c>
-      <c r="D30" t="s">
-        <v>197</v>
-      </c>
-      <c r="E30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F30" t="s">
-        <v>42</v>
-      </c>
-      <c r="G30" t="s">
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>577</v>
+      </c>
+      <c r="B40" t="s">
+        <v>898</v>
+      </c>
+      <c r="C40" s="19">
+        <v>31585</v>
+      </c>
+      <c r="D40" t="s">
+        <v>362</v>
+      </c>
+      <c r="E40" t="s">
+        <v>369</v>
+      </c>
+      <c r="F40" t="s">
         <v>67</v>
       </c>
-      <c r="H30" s="3">
-        <v>50</v>
-      </c>
-      <c r="J30" t="s">
-        <v>278</v>
-      </c>
-      <c r="K30">
-        <v>60</v>
-      </c>
-      <c r="L30" t="s">
-        <v>697</v>
-      </c>
-      <c r="M30">
-        <f>COUNTIF(Tabela2[Mapa],J30)</f>
-        <v>3</v>
-      </c>
-      <c r="N30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" t="s">
-        <v>713</v>
-      </c>
-      <c r="B31" s="19">
-        <v>30238</v>
-      </c>
-      <c r="C31" t="s">
-        <v>185</v>
-      </c>
-      <c r="D31" t="s">
-        <v>178</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="G40" t="s">
+        <v>42</v>
+      </c>
+      <c r="H40" t="s">
+        <v>42</v>
+      </c>
+      <c r="I40" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>733</v>
+      </c>
+      <c r="B41" t="s">
+        <v>900</v>
+      </c>
+      <c r="C41" s="19">
+        <v>33335</v>
+      </c>
+      <c r="D41" t="s">
+        <v>340</v>
+      </c>
+      <c r="E41" t="s">
+        <v>249</v>
+      </c>
+      <c r="F41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G41" t="s">
         <v>27</v>
       </c>
-      <c r="F31" t="s">
+      <c r="H41" t="s">
         <v>27</v>
       </c>
-      <c r="G31" t="s">
+      <c r="I41" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>779</v>
+      </c>
+      <c r="B42" t="s">
+        <v>899</v>
+      </c>
+      <c r="C42" s="19">
+        <v>36662</v>
+      </c>
+      <c r="D42" t="s">
+        <v>397</v>
+      </c>
+      <c r="E42" t="s">
+        <v>705</v>
+      </c>
+      <c r="F42" t="s">
         <v>117</v>
       </c>
-      <c r="H31" s="3">
-        <v>150</v>
-      </c>
-      <c r="J31" t="s">
-        <v>298</v>
-      </c>
-      <c r="K31">
-        <v>60</v>
-      </c>
-      <c r="L31" t="s">
-        <v>697</v>
-      </c>
-      <c r="M31">
-        <f>COUNTIF(Tabela2[Mapa],J31)</f>
-        <v>3</v>
-      </c>
-      <c r="N31">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" t="s">
-        <v>714</v>
-      </c>
-      <c r="B32" s="19">
-        <v>37715</v>
-      </c>
-      <c r="C32" t="s">
-        <v>185</v>
-      </c>
-      <c r="D32" t="s">
-        <v>178</v>
-      </c>
-      <c r="E32" t="s">
-        <v>27</v>
-      </c>
-      <c r="F32" t="s">
-        <v>42</v>
-      </c>
-      <c r="G32" t="s">
-        <v>41</v>
-      </c>
-      <c r="H32" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" t="s">
-        <v>715</v>
-      </c>
-      <c r="B33" s="19">
-        <v>43240</v>
-      </c>
-      <c r="C33" t="s">
-        <v>185</v>
-      </c>
-      <c r="D33" t="s">
-        <v>178</v>
-      </c>
-      <c r="E33" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" t="s">
-        <v>27</v>
-      </c>
-      <c r="G33" t="s">
-        <v>27</v>
-      </c>
-      <c r="H33" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>716</v>
-      </c>
-      <c r="B34" s="19">
-        <v>36620</v>
-      </c>
-      <c r="C34" t="s">
-        <v>483</v>
-      </c>
-      <c r="D34" t="s">
-        <v>488</v>
-      </c>
-      <c r="E34" t="s">
-        <v>42</v>
-      </c>
-      <c r="F34" t="s">
-        <v>27</v>
-      </c>
-      <c r="G34" t="s">
-        <v>27</v>
-      </c>
-      <c r="H34" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>717</v>
-      </c>
-      <c r="B35" s="19">
-        <v>40580</v>
-      </c>
-      <c r="C35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D35" t="s">
-        <v>156</v>
-      </c>
-      <c r="E35" t="s">
-        <v>41</v>
-      </c>
-      <c r="F35" t="s">
-        <v>41</v>
-      </c>
-      <c r="G35" t="s">
-        <v>42</v>
-      </c>
-      <c r="H35" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" t="s">
-        <v>577</v>
-      </c>
-      <c r="B36" s="19">
-        <v>31585</v>
-      </c>
-      <c r="C36" t="s">
-        <v>362</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="G42" t="s">
+        <v>117</v>
+      </c>
+      <c r="H42" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>789</v>
+      </c>
+      <c r="B43" t="s">
+        <v>901</v>
+      </c>
+      <c r="C43" s="19">
+        <v>34189</v>
+      </c>
+      <c r="D43" t="s">
         <v>369</v>
       </c>
-      <c r="E36" t="s">
-        <v>67</v>
-      </c>
-      <c r="F36" t="s">
-        <v>42</v>
-      </c>
-      <c r="G36" t="s">
-        <v>42</v>
-      </c>
-      <c r="H36" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" t="s">
-        <v>718</v>
-      </c>
-      <c r="B37" s="19">
-        <v>37155</v>
-      </c>
-      <c r="C37" t="s">
-        <v>362</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="E43" t="s">
         <v>369</v>
-      </c>
-      <c r="E37" t="s">
-        <v>42</v>
-      </c>
-      <c r="F37" t="s">
-        <v>67</v>
-      </c>
-      <c r="G37" t="s">
-        <v>67</v>
-      </c>
-      <c r="H37" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" t="s">
-        <v>719</v>
-      </c>
-      <c r="B38" s="19">
-        <v>25385</v>
-      </c>
-      <c r="C38" t="s">
-        <v>53</v>
-      </c>
-      <c r="D38" t="s">
-        <v>38</v>
-      </c>
-      <c r="E38" t="s">
-        <v>27</v>
-      </c>
-      <c r="F38" t="s">
-        <v>27</v>
-      </c>
-      <c r="G38" t="s">
-        <v>42</v>
-      </c>
-      <c r="H38" s="3">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" t="s">
-        <v>720</v>
-      </c>
-      <c r="B39" s="19">
-        <v>26153</v>
-      </c>
-      <c r="C39" t="s">
-        <v>53</v>
-      </c>
-      <c r="D39" t="s">
-        <v>38</v>
-      </c>
-      <c r="E39" t="s">
-        <v>42</v>
-      </c>
-      <c r="F39" t="s">
-        <v>27</v>
-      </c>
-      <c r="G39" t="s">
-        <v>708</v>
-      </c>
-      <c r="H39" s="3">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" t="s">
-        <v>721</v>
-      </c>
-      <c r="B40" s="19">
-        <v>33125</v>
-      </c>
-      <c r="C40" t="s">
-        <v>53</v>
-      </c>
-      <c r="D40" t="s">
-        <v>38</v>
-      </c>
-      <c r="E40" t="s">
-        <v>27</v>
-      </c>
-      <c r="F40" t="s">
-        <v>42</v>
-      </c>
-      <c r="G40" t="s">
-        <v>42</v>
-      </c>
-      <c r="H40" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" t="s">
-        <v>722</v>
-      </c>
-      <c r="B41" s="19">
-        <v>28400</v>
-      </c>
-      <c r="C41" t="s">
-        <v>158</v>
-      </c>
-      <c r="D41" t="s">
-        <v>132</v>
-      </c>
-      <c r="E41" t="s">
-        <v>41</v>
-      </c>
-      <c r="F41" t="s">
-        <v>41</v>
-      </c>
-      <c r="G41" t="s">
-        <v>42</v>
-      </c>
-      <c r="H41" s="3">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" t="s">
-        <v>723</v>
-      </c>
-      <c r="B42" s="19">
-        <v>35125</v>
-      </c>
-      <c r="C42" t="s">
-        <v>158</v>
-      </c>
-      <c r="D42" t="s">
-        <v>132</v>
-      </c>
-      <c r="E42" t="s">
-        <v>42</v>
-      </c>
-      <c r="F42" t="s">
-        <v>41</v>
-      </c>
-      <c r="G42" t="s">
-        <v>41</v>
-      </c>
-      <c r="H42" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" t="s">
-        <v>724</v>
-      </c>
-      <c r="B43" s="19">
-        <v>34192</v>
-      </c>
-      <c r="C43" t="s">
-        <v>250</v>
-      </c>
-      <c r="D43" t="s">
-        <v>257</v>
-      </c>
-      <c r="E43" t="s">
-        <v>26</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
@@ -10948,517 +11452,579 @@
       <c r="G43" t="s">
         <v>42</v>
       </c>
-      <c r="H43" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="H43" t="s">
+        <v>42</v>
+      </c>
+      <c r="I43" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>725</v>
-      </c>
-      <c r="B44" s="19">
-        <v>39640</v>
-      </c>
-      <c r="C44" t="s">
-        <v>250</v>
+        <v>703</v>
+      </c>
+      <c r="B44" t="s">
+        <v>861</v>
+      </c>
+      <c r="C44" s="19">
+        <v>39675</v>
       </c>
       <c r="D44" t="s">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="E44" t="s">
-        <v>26</v>
+        <v>306</v>
       </c>
       <c r="F44" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="G44" t="s">
-        <v>117</v>
-      </c>
-      <c r="H44" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="H44" t="s">
+        <v>42</v>
+      </c>
+      <c r="I44" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>726</v>
-      </c>
-      <c r="B45" s="19">
-        <v>33377</v>
-      </c>
-      <c r="C45" t="s">
-        <v>236</v>
+        <v>704</v>
+      </c>
+      <c r="B45" t="s">
+        <v>862</v>
+      </c>
+      <c r="C45" s="19">
+        <v>35512</v>
       </c>
       <c r="D45" t="s">
-        <v>156</v>
+        <v>299</v>
       </c>
       <c r="E45" t="s">
-        <v>117</v>
+        <v>306</v>
       </c>
       <c r="F45" t="s">
         <v>27</v>
       </c>
       <c r="G45" t="s">
+        <v>42</v>
+      </c>
+      <c r="H45" t="s">
+        <v>42</v>
+      </c>
+      <c r="I45" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>709</v>
+      </c>
+      <c r="B46" t="s">
+        <v>859</v>
+      </c>
+      <c r="C46" s="19">
+        <v>35898</v>
+      </c>
+      <c r="D46" t="s">
+        <v>355</v>
+      </c>
+      <c r="E46" t="s">
+        <v>197</v>
+      </c>
+      <c r="F46" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" t="s">
+        <v>42</v>
+      </c>
+      <c r="H46" t="s">
         <v>27</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I46" s="3">
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
-      <c r="A46" t="s">
-        <v>727</v>
-      </c>
-      <c r="B46" s="19">
-        <v>28281</v>
-      </c>
-      <c r="C46" t="s">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>711</v>
+      </c>
+      <c r="B47" t="s">
+        <v>864</v>
+      </c>
+      <c r="C47" s="19">
+        <v>37696</v>
+      </c>
+      <c r="D47" t="s">
+        <v>381</v>
+      </c>
+      <c r="E47" t="s">
+        <v>306</v>
+      </c>
+      <c r="F47" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" t="s">
+        <v>26</v>
+      </c>
+      <c r="H47" t="s">
+        <v>27</v>
+      </c>
+      <c r="I47" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>721</v>
+      </c>
+      <c r="B48" t="s">
+        <v>897</v>
+      </c>
+      <c r="C48" s="19">
+        <v>33125</v>
+      </c>
+      <c r="D48" t="s">
+        <v>53</v>
+      </c>
+      <c r="E48" t="s">
+        <v>38</v>
+      </c>
+      <c r="F48" t="s">
+        <v>27</v>
+      </c>
+      <c r="G48" t="s">
+        <v>42</v>
+      </c>
+      <c r="H48" t="s">
+        <v>42</v>
+      </c>
+      <c r="I48" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>726</v>
+      </c>
+      <c r="B49" t="s">
+        <v>892</v>
+      </c>
+      <c r="C49" s="19">
+        <v>33377</v>
+      </c>
+      <c r="D49" t="s">
+        <v>236</v>
+      </c>
+      <c r="E49" t="s">
+        <v>156</v>
+      </c>
+      <c r="F49" t="s">
+        <v>117</v>
+      </c>
+      <c r="G49" t="s">
+        <v>27</v>
+      </c>
+      <c r="H49" t="s">
+        <v>27</v>
+      </c>
+      <c r="I49" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>728</v>
+      </c>
+      <c r="B50" t="s">
+        <v>902</v>
+      </c>
+      <c r="C50" s="19">
+        <v>35731</v>
+      </c>
+      <c r="D50" t="s">
         <v>93</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E50" t="s">
         <v>89</v>
       </c>
-      <c r="E46" t="s">
-        <v>42</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="F50" t="s">
         <v>67</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G50" t="s">
         <v>67</v>
       </c>
-      <c r="H46" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" t="s">
-        <v>728</v>
-      </c>
-      <c r="B47" s="19">
-        <v>35731</v>
-      </c>
-      <c r="C47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D47" t="s">
-        <v>89</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="H50" t="s">
+        <v>42</v>
+      </c>
+      <c r="I50" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>743</v>
+      </c>
+      <c r="B51" t="s">
+        <v>893</v>
+      </c>
+      <c r="C51" s="19">
+        <v>29852</v>
+      </c>
+      <c r="D51" t="s">
+        <v>104</v>
+      </c>
+      <c r="E51" t="s">
+        <v>108</v>
+      </c>
+      <c r="F51" t="s">
         <v>67</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G51" t="s">
         <v>67</v>
       </c>
-      <c r="G47" t="s">
-        <v>42</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H51" t="s">
+        <v>27</v>
+      </c>
+      <c r="I51" s="3">
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
-      <c r="A48" t="s">
-        <v>729</v>
-      </c>
-      <c r="B48" s="19">
-        <v>40323</v>
-      </c>
-      <c r="C48" t="s">
-        <v>443</v>
-      </c>
-      <c r="D48" t="s">
-        <v>257</v>
-      </c>
-      <c r="E48" t="s">
-        <v>694</v>
-      </c>
-      <c r="F48" t="s">
-        <v>42</v>
-      </c>
-      <c r="G48" t="s">
-        <v>42</v>
-      </c>
-      <c r="H48" s="3"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" t="s">
-        <v>730</v>
-      </c>
-      <c r="B49" s="19">
-        <v>33900</v>
-      </c>
-      <c r="C49" t="s">
-        <v>443</v>
-      </c>
-      <c r="D49" t="s">
-        <v>257</v>
-      </c>
-      <c r="E49" t="s">
-        <v>42</v>
-      </c>
-      <c r="F49" t="s">
-        <v>694</v>
-      </c>
-      <c r="G49" t="s">
-        <v>694</v>
-      </c>
-      <c r="H49" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" t="s">
-        <v>731</v>
-      </c>
-      <c r="B50" s="19">
-        <v>40596</v>
-      </c>
-      <c r="C50" t="s">
-        <v>223</v>
-      </c>
-      <c r="D50" t="s">
-        <v>228</v>
-      </c>
-      <c r="E50" t="s">
-        <v>117</v>
-      </c>
-      <c r="F50" t="s">
-        <v>41</v>
-      </c>
-      <c r="G50" t="s">
-        <v>42</v>
-      </c>
-      <c r="H50" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" t="s">
-        <v>732</v>
-      </c>
-      <c r="B51" s="19">
-        <v>33181</v>
-      </c>
-      <c r="C51" t="s">
-        <v>344</v>
-      </c>
-      <c r="D51" t="s">
-        <v>178</v>
-      </c>
-      <c r="E51" t="s">
-        <v>42</v>
-      </c>
-      <c r="F51" t="s">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>749</v>
+      </c>
+      <c r="B52" t="s">
+        <v>903</v>
+      </c>
+      <c r="C52" s="19">
+        <v>33812</v>
+      </c>
+      <c r="D52" t="s">
+        <v>142</v>
+      </c>
+      <c r="E52" t="s">
+        <v>108</v>
+      </c>
+      <c r="F52" t="s">
+        <v>42</v>
+      </c>
+      <c r="G52" t="s">
+        <v>42</v>
+      </c>
+      <c r="H52" t="s">
+        <v>26</v>
+      </c>
+      <c r="I52" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>751</v>
+      </c>
+      <c r="B53" t="s">
+        <v>894</v>
+      </c>
+      <c r="C53" s="19">
+        <v>37179</v>
+      </c>
+      <c r="D53" t="s">
+        <v>465</v>
+      </c>
+      <c r="E53" t="s">
+        <v>156</v>
+      </c>
+      <c r="F53" t="s">
         <v>27</v>
-      </c>
-      <c r="G51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H51" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" t="s">
-        <v>733</v>
-      </c>
-      <c r="B52" s="19">
-        <v>33335</v>
-      </c>
-      <c r="C52" t="s">
-        <v>340</v>
-      </c>
-      <c r="D52" t="s">
-        <v>249</v>
-      </c>
-      <c r="E52" t="s">
-        <v>42</v>
-      </c>
-      <c r="F52" t="s">
-        <v>27</v>
-      </c>
-      <c r="G52" t="s">
-        <v>27</v>
-      </c>
-      <c r="H52" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" t="s">
-        <v>734</v>
-      </c>
-      <c r="B53" s="19">
-        <v>24812</v>
-      </c>
-      <c r="C53" t="s">
-        <v>19</v>
-      </c>
-      <c r="D53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E53" t="s">
-        <v>42</v>
-      </c>
-      <c r="F53" t="s">
-        <v>26</v>
       </c>
       <c r="G53" t="s">
         <v>27</v>
       </c>
-      <c r="H53" s="3">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+      <c r="H53" t="s">
+        <v>42</v>
+      </c>
+      <c r="I53" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>735</v>
-      </c>
-      <c r="B54" s="19">
-        <v>28239</v>
-      </c>
-      <c r="C54" t="s">
-        <v>19</v>
+        <v>766</v>
+      </c>
+      <c r="B54" t="s">
+        <v>766</v>
+      </c>
+      <c r="C54" s="19">
+        <v>25901</v>
       </c>
       <c r="D54" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F54" t="s">
+        <v>41</v>
+      </c>
+      <c r="G54" t="s">
+        <v>41</v>
+      </c>
+      <c r="H54" t="s">
+        <v>42</v>
+      </c>
+      <c r="I54" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>771</v>
+      </c>
+      <c r="B55" t="s">
+        <v>890</v>
+      </c>
+      <c r="C55" s="19">
+        <v>25285</v>
+      </c>
+      <c r="D55" t="s">
+        <v>267</v>
+      </c>
+      <c r="E55" t="s">
+        <v>127</v>
+      </c>
+      <c r="F55" t="s">
+        <v>42</v>
+      </c>
+      <c r="G55" t="s">
+        <v>27</v>
+      </c>
+      <c r="H55" t="s">
+        <v>27</v>
+      </c>
+      <c r="I55" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>788</v>
+      </c>
+      <c r="B56" t="s">
+        <v>833</v>
+      </c>
+      <c r="C56" s="19">
+        <v>30848</v>
+      </c>
+      <c r="D56" t="s">
+        <v>38</v>
+      </c>
+      <c r="E56" t="s">
+        <v>38</v>
+      </c>
+      <c r="F56" t="s">
         <v>26</v>
-      </c>
-      <c r="F54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" t="s">
-        <v>27</v>
-      </c>
-      <c r="H54" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" t="s">
-        <v>736</v>
-      </c>
-      <c r="B55" s="19">
-        <v>25914</v>
-      </c>
-      <c r="C55" t="s">
-        <v>71</v>
-      </c>
-      <c r="D55" t="s">
-        <v>23</v>
-      </c>
-      <c r="E55" t="s">
-        <v>42</v>
-      </c>
-      <c r="F55" t="s">
-        <v>41</v>
-      </c>
-      <c r="G55" t="s">
-        <v>41</v>
-      </c>
-      <c r="H55" s="3">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" t="s">
-        <v>737</v>
-      </c>
-      <c r="B56" s="19">
-        <v>25897</v>
-      </c>
-      <c r="C56" t="s">
-        <v>71</v>
-      </c>
-      <c r="D56" t="s">
-        <v>23</v>
-      </c>
-      <c r="E56" t="s">
-        <v>41</v>
-      </c>
-      <c r="F56" t="s">
-        <v>41</v>
       </c>
       <c r="G56" t="s">
         <v>26</v>
       </c>
-      <c r="H56" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+      <c r="H56" t="s">
+        <v>42</v>
+      </c>
+      <c r="I56" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>738</v>
-      </c>
-      <c r="B57" s="19">
-        <v>33286</v>
-      </c>
-      <c r="C57" t="s">
+        <v>793</v>
+      </c>
+      <c r="B57" t="s">
+        <v>872</v>
+      </c>
+      <c r="C57" s="19">
+        <v>37238</v>
+      </c>
+      <c r="D57" t="s">
+        <v>376</v>
+      </c>
+      <c r="E57" t="s">
+        <v>306</v>
+      </c>
+      <c r="F57" t="s">
+        <v>42</v>
+      </c>
+      <c r="G57" t="s">
+        <v>42</v>
+      </c>
+      <c r="H57" t="s">
+        <v>27</v>
+      </c>
+      <c r="I57" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>796</v>
+      </c>
+      <c r="B58" t="s">
+        <v>895</v>
+      </c>
+      <c r="C58" s="19">
+        <v>38759</v>
+      </c>
+      <c r="D58" t="s">
+        <v>136</v>
+      </c>
+      <c r="E58" t="s">
+        <v>23</v>
+      </c>
+      <c r="F58" t="s">
+        <v>27</v>
+      </c>
+      <c r="G58" t="s">
+        <v>42</v>
+      </c>
+      <c r="H58" t="s">
+        <v>42</v>
+      </c>
+      <c r="I58" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>691</v>
+      </c>
+      <c r="B59" t="s">
+        <v>841</v>
+      </c>
+      <c r="C59" s="19">
+        <v>32899</v>
+      </c>
+      <c r="D59" t="s">
+        <v>85</v>
+      </c>
+      <c r="E59" t="s">
+        <v>89</v>
+      </c>
+      <c r="F59" t="s">
+        <v>27</v>
+      </c>
+      <c r="G59" t="s">
+        <v>27</v>
+      </c>
+      <c r="H59" t="s">
+        <v>42</v>
+      </c>
+      <c r="I59" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B60" t="s">
+        <v>834</v>
+      </c>
+      <c r="C60" s="19">
+        <v>34398</v>
+      </c>
+      <c r="D60" t="s">
+        <v>385</v>
+      </c>
+      <c r="E60" t="s">
+        <v>197</v>
+      </c>
+      <c r="F60" t="s">
+        <v>75</v>
+      </c>
+      <c r="G60" t="s">
+        <v>42</v>
+      </c>
+      <c r="H60" t="s">
+        <v>67</v>
+      </c>
+      <c r="I60" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>753</v>
+      </c>
+      <c r="B61" t="s">
+        <v>905</v>
+      </c>
+      <c r="C61" s="19">
+        <v>33639</v>
+      </c>
+      <c r="D61" t="s">
+        <v>239</v>
+      </c>
+      <c r="E61" t="s">
+        <v>244</v>
+      </c>
+      <c r="F61" t="s">
+        <v>694</v>
+      </c>
+      <c r="G61" t="s">
+        <v>42</v>
+      </c>
+      <c r="H61" t="s">
+        <v>694</v>
+      </c>
+      <c r="I61" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>698</v>
+      </c>
+      <c r="B62" t="s">
+        <v>854</v>
+      </c>
+      <c r="C62" s="19">
+        <v>32607</v>
+      </c>
+      <c r="D62" t="s">
+        <v>60</v>
+      </c>
+      <c r="E62" t="s">
+        <v>60</v>
+      </c>
+      <c r="F62" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H62" t="s">
+        <v>695</v>
+      </c>
+      <c r="I62" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>714</v>
+      </c>
+      <c r="B63" t="s">
+        <v>714</v>
+      </c>
+      <c r="C63" s="19">
+        <v>37715</v>
+      </c>
+      <c r="D63" t="s">
+        <v>185</v>
+      </c>
+      <c r="E63" t="s">
         <v>178</v>
-      </c>
-      <c r="D57" t="s">
-        <v>178</v>
-      </c>
-      <c r="E57" t="s">
-        <v>42</v>
-      </c>
-      <c r="F57" t="s">
-        <v>42</v>
-      </c>
-      <c r="G57" t="s">
-        <v>67</v>
-      </c>
-      <c r="H57" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" t="s">
-        <v>739</v>
-      </c>
-      <c r="B58" s="19">
-        <v>35356</v>
-      </c>
-      <c r="C58" t="s">
-        <v>178</v>
-      </c>
-      <c r="D58" t="s">
-        <v>178</v>
-      </c>
-      <c r="E58" t="s">
-        <v>67</v>
-      </c>
-      <c r="F58" t="s">
-        <v>67</v>
-      </c>
-      <c r="G58" t="s">
-        <v>26</v>
-      </c>
-      <c r="H58" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" t="s">
-        <v>740</v>
-      </c>
-      <c r="B59" s="19">
-        <v>37683</v>
-      </c>
-      <c r="C59" t="s">
-        <v>404</v>
-      </c>
-      <c r="D59" t="s">
-        <v>409</v>
-      </c>
-      <c r="E59" t="s">
-        <v>41</v>
-      </c>
-      <c r="F59" t="s">
-        <v>41</v>
-      </c>
-      <c r="G59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H59" s="3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" t="s">
-        <v>741</v>
-      </c>
-      <c r="B60" s="19">
-        <v>35573</v>
-      </c>
-      <c r="C60" t="s">
-        <v>198</v>
-      </c>
-      <c r="D60" t="s">
-        <v>202</v>
-      </c>
-      <c r="E60" t="s">
-        <v>41</v>
-      </c>
-      <c r="F60" t="s">
-        <v>41</v>
-      </c>
-      <c r="G60" t="s">
-        <v>42</v>
-      </c>
-      <c r="H60" s="3">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" t="s">
-        <v>742</v>
-      </c>
-      <c r="B61" s="19">
-        <v>39938</v>
-      </c>
-      <c r="C61" t="s">
-        <v>554</v>
-      </c>
-      <c r="D61" t="s">
-        <v>442</v>
-      </c>
-      <c r="E61" t="s">
-        <v>694</v>
-      </c>
-      <c r="F61" t="s">
-        <v>42</v>
-      </c>
-      <c r="G61" t="s">
-        <v>42</v>
-      </c>
-      <c r="H61" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" t="s">
-        <v>743</v>
-      </c>
-      <c r="B62" s="19">
-        <v>29852</v>
-      </c>
-      <c r="C62" t="s">
-        <v>104</v>
-      </c>
-      <c r="D62" t="s">
-        <v>108</v>
-      </c>
-      <c r="E62" t="s">
-        <v>67</v>
-      </c>
-      <c r="F62" t="s">
-        <v>67</v>
-      </c>
-      <c r="G62" t="s">
-        <v>27</v>
-      </c>
-      <c r="H62" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" t="s">
-        <v>744</v>
-      </c>
-      <c r="B63" s="19">
-        <v>28421</v>
-      </c>
-      <c r="C63" t="s">
-        <v>104</v>
-      </c>
-      <c r="D63" t="s">
-        <v>108</v>
-      </c>
-      <c r="E63" t="s">
-        <v>67</v>
       </c>
       <c r="F63" t="s">
         <v>27</v>
@@ -11466,103 +12032,115 @@
       <c r="G63" t="s">
         <v>42</v>
       </c>
-      <c r="H63" s="3">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+      <c r="H63" t="s">
+        <v>41</v>
+      </c>
+      <c r="I63" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>745</v>
-      </c>
-      <c r="B64" s="19">
-        <v>34241</v>
-      </c>
-      <c r="C64" t="s">
-        <v>307</v>
+        <v>739</v>
+      </c>
+      <c r="B64" t="s">
+        <v>906</v>
+      </c>
+      <c r="C64" s="19">
+        <v>35356</v>
       </c>
       <c r="D64" t="s">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="E64" t="s">
-        <v>42</v>
+        <v>178</v>
       </c>
       <c r="F64" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="G64" t="s">
-        <v>41</v>
-      </c>
-      <c r="H64" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <v>67</v>
+      </c>
+      <c r="H64" t="s">
+        <v>26</v>
+      </c>
+      <c r="I64" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>746</v>
-      </c>
-      <c r="B65" s="19">
-        <v>36905</v>
-      </c>
-      <c r="C65" t="s">
-        <v>476</v>
+        <v>781</v>
+      </c>
+      <c r="B65" t="s">
+        <v>831</v>
+      </c>
+      <c r="C65" s="19">
+        <v>39396</v>
       </c>
       <c r="D65" t="s">
-        <v>454</v>
+        <v>284</v>
       </c>
       <c r="E65" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="F65" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G65" t="s">
         <v>26</v>
       </c>
-      <c r="H65" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+      <c r="H65" t="s">
+        <v>42</v>
+      </c>
+      <c r="I65" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>747</v>
-      </c>
-      <c r="B66" s="19">
-        <v>38671</v>
-      </c>
-      <c r="C66" t="s">
-        <v>447</v>
+        <v>792</v>
+      </c>
+      <c r="B66" t="s">
+        <v>904</v>
+      </c>
+      <c r="C66" s="19">
+        <v>32440</v>
       </c>
       <c r="D66" t="s">
-        <v>454</v>
+        <v>206</v>
       </c>
       <c r="E66" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="F66" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>41</v>
-      </c>
-      <c r="H66" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="H66" t="s">
+        <v>27</v>
+      </c>
+      <c r="I66" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>748</v>
-      </c>
-      <c r="B67" s="19">
-        <v>32964</v>
-      </c>
-      <c r="C67" t="s">
-        <v>391</v>
+        <v>686</v>
+      </c>
+      <c r="B67" t="s">
+        <v>844</v>
+      </c>
+      <c r="C67" s="19">
+        <v>36754</v>
       </c>
       <c r="D67" t="s">
-        <v>119</v>
+        <v>431</v>
       </c>
       <c r="E67" t="s">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="F67" t="s">
         <v>27</v>
@@ -11570,441 +12148,492 @@
       <c r="G67" t="s">
         <v>27</v>
       </c>
-      <c r="H67" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+      <c r="H67" t="s">
+        <v>42</v>
+      </c>
+      <c r="I67" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>749</v>
-      </c>
-      <c r="B68" s="19">
-        <v>33812</v>
-      </c>
-      <c r="C68" t="s">
-        <v>142</v>
+        <v>692</v>
+      </c>
+      <c r="B68" t="s">
+        <v>852</v>
+      </c>
+      <c r="C68" s="19">
+        <v>40011</v>
       </c>
       <c r="D68" t="s">
-        <v>108</v>
+        <v>213</v>
       </c>
       <c r="E68" t="s">
-        <v>42</v>
+        <v>202</v>
       </c>
       <c r="F68" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>26</v>
-      </c>
-      <c r="H68" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="H68" t="s">
+        <v>42</v>
+      </c>
+      <c r="I68" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>750</v>
-      </c>
-      <c r="B69" s="19">
-        <v>25488</v>
-      </c>
-      <c r="C69" t="s">
-        <v>142</v>
+        <v>706</v>
+      </c>
+      <c r="B69" t="s">
+        <v>858</v>
+      </c>
+      <c r="C69" s="19">
+        <v>33639</v>
       </c>
       <c r="D69" t="s">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="E69" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="F69" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="G69" t="s">
         <v>26</v>
       </c>
-      <c r="H69" s="3">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
+      <c r="H69" t="s">
+        <v>27</v>
+      </c>
+      <c r="I69" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>751</v>
-      </c>
-      <c r="B70" s="19">
-        <v>37179</v>
-      </c>
-      <c r="C70" t="s">
-        <v>465</v>
+        <v>716</v>
+      </c>
+      <c r="B70" t="s">
+        <v>888</v>
+      </c>
+      <c r="C70" s="19">
+        <v>36620</v>
       </c>
       <c r="D70" t="s">
+        <v>483</v>
+      </c>
+      <c r="E70" t="s">
+        <v>488</v>
+      </c>
+      <c r="F70" t="s">
+        <v>42</v>
+      </c>
+      <c r="G70" t="s">
+        <v>27</v>
+      </c>
+      <c r="H70" t="s">
+        <v>27</v>
+      </c>
+      <c r="I70" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>718</v>
+      </c>
+      <c r="B71" t="s">
+        <v>907</v>
+      </c>
+      <c r="C71" s="19">
+        <v>37155</v>
+      </c>
+      <c r="D71" t="s">
+        <v>362</v>
+      </c>
+      <c r="E71" t="s">
+        <v>369</v>
+      </c>
+      <c r="F71" t="s">
+        <v>42</v>
+      </c>
+      <c r="G71" t="s">
+        <v>67</v>
+      </c>
+      <c r="H71" t="s">
+        <v>67</v>
+      </c>
+      <c r="I71" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>746</v>
+      </c>
+      <c r="B72" t="s">
+        <v>873</v>
+      </c>
+      <c r="C72" s="19">
+        <v>36905</v>
+      </c>
+      <c r="D72" t="s">
+        <v>476</v>
+      </c>
+      <c r="E72" t="s">
+        <v>454</v>
+      </c>
+      <c r="F72" t="s">
+        <v>42</v>
+      </c>
+      <c r="G72" t="s">
+        <v>27</v>
+      </c>
+      <c r="H72" t="s">
+        <v>26</v>
+      </c>
+      <c r="I72" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>747</v>
+      </c>
+      <c r="B73" t="s">
+        <v>889</v>
+      </c>
+      <c r="C73" s="19">
+        <v>38671</v>
+      </c>
+      <c r="D73" t="s">
+        <v>447</v>
+      </c>
+      <c r="E73" t="s">
+        <v>454</v>
+      </c>
+      <c r="F73" t="s">
+        <v>42</v>
+      </c>
+      <c r="G73" t="s">
+        <v>41</v>
+      </c>
+      <c r="H73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I73" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>759</v>
+      </c>
+      <c r="B74" t="s">
+        <v>911</v>
+      </c>
+      <c r="C74" s="19">
+        <v>35358</v>
+      </c>
+      <c r="D74" t="s">
+        <v>425</v>
+      </c>
+      <c r="E74" t="s">
+        <v>705</v>
+      </c>
+      <c r="F74" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" t="s">
+        <v>26</v>
+      </c>
+      <c r="H74" t="s">
+        <v>27</v>
+      </c>
+      <c r="I74" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>760</v>
+      </c>
+      <c r="B75" t="s">
+        <v>912</v>
+      </c>
+      <c r="C75" s="19">
+        <v>33494</v>
+      </c>
+      <c r="D75" t="s">
+        <v>469</v>
+      </c>
+      <c r="E75" t="s">
+        <v>352</v>
+      </c>
+      <c r="F75" t="s">
+        <v>67</v>
+      </c>
+      <c r="G75" t="s">
+        <v>67</v>
+      </c>
+      <c r="H75" t="s">
+        <v>42</v>
+      </c>
+      <c r="I75" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>764</v>
+      </c>
+      <c r="B76" t="s">
+        <v>899</v>
+      </c>
+      <c r="C76" s="19">
+        <v>31048</v>
+      </c>
+      <c r="D76" t="s">
+        <v>285</v>
+      </c>
+      <c r="E76" t="s">
+        <v>244</v>
+      </c>
+      <c r="F76" t="s">
+        <v>42</v>
+      </c>
+      <c r="G76" t="s">
+        <v>27</v>
+      </c>
+      <c r="H76" t="s">
+        <v>27</v>
+      </c>
+      <c r="I76" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>770</v>
+      </c>
+      <c r="B77" t="s">
+        <v>908</v>
+      </c>
+      <c r="C77" s="19">
+        <v>34108</v>
+      </c>
+      <c r="D77" t="s">
+        <v>359</v>
+      </c>
+      <c r="E77" t="s">
+        <v>197</v>
+      </c>
+      <c r="F77" t="s">
+        <v>117</v>
+      </c>
+      <c r="G77" t="s">
+        <v>67</v>
+      </c>
+      <c r="H77" t="s">
+        <v>67</v>
+      </c>
+      <c r="I77" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>812</v>
+      </c>
+      <c r="B78" t="s">
+        <v>914</v>
+      </c>
+      <c r="C78" s="19">
+        <v>35836</v>
+      </c>
+      <c r="D78" t="s">
+        <v>641</v>
+      </c>
+      <c r="E78" t="s">
+        <v>369</v>
+      </c>
+      <c r="F78" t="s">
+        <v>67</v>
+      </c>
+      <c r="G78" t="s">
+        <v>26</v>
+      </c>
+      <c r="H78" t="s">
+        <v>42</v>
+      </c>
+      <c r="I78" s="20">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>813</v>
+      </c>
+      <c r="B79" t="s">
+        <v>916</v>
+      </c>
+      <c r="C79" s="19">
+        <v>38431</v>
+      </c>
+      <c r="D79" t="s">
+        <v>647</v>
+      </c>
+      <c r="E79" t="s">
+        <v>488</v>
+      </c>
+      <c r="F79" t="s">
+        <v>42</v>
+      </c>
+      <c r="G79" t="s">
+        <v>41</v>
+      </c>
+      <c r="H79" t="s">
+        <v>26</v>
+      </c>
+      <c r="I79" s="20">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>817</v>
+      </c>
+      <c r="B80" t="s">
+        <v>917</v>
+      </c>
+      <c r="C80" s="19">
+        <v>37080</v>
+      </c>
+      <c r="D80" t="s">
+        <v>607</v>
+      </c>
+      <c r="E80" t="s">
+        <v>705</v>
+      </c>
+      <c r="F80" t="s">
+        <v>42</v>
+      </c>
+      <c r="G80" t="s">
+        <v>42</v>
+      </c>
+      <c r="H80" t="s">
+        <v>27</v>
+      </c>
+      <c r="I80" s="20">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>680</v>
+      </c>
+      <c r="B81" t="s">
+        <v>835</v>
+      </c>
+      <c r="C81" s="19">
+        <v>43831</v>
+      </c>
+      <c r="D81" t="s">
+        <v>349</v>
+      </c>
+      <c r="E81" t="s">
+        <v>352</v>
+      </c>
+      <c r="F81" t="s">
+        <v>117</v>
+      </c>
+      <c r="G81" t="s">
+        <v>27</v>
+      </c>
+      <c r="H81" t="s">
+        <v>27</v>
+      </c>
+      <c r="I81" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>699</v>
+      </c>
+      <c r="B82" t="s">
+        <v>855</v>
+      </c>
+      <c r="C82" s="19">
+        <v>37306</v>
+      </c>
+      <c r="D82" t="s">
+        <v>518</v>
+      </c>
+      <c r="E82" t="s">
+        <v>442</v>
+      </c>
+      <c r="F82" t="s">
+        <v>42</v>
+      </c>
+      <c r="G82" t="s">
+        <v>26</v>
+      </c>
+      <c r="H82" t="s">
+        <v>26</v>
+      </c>
+      <c r="I82" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>717</v>
+      </c>
+      <c r="B83" t="s">
+        <v>907</v>
+      </c>
+      <c r="C83" s="19">
+        <v>40580</v>
+      </c>
+      <c r="D83" t="s">
+        <v>148</v>
+      </c>
+      <c r="E83" t="s">
         <v>156</v>
       </c>
-      <c r="E70" t="s">
-        <v>27</v>
-      </c>
-      <c r="F70" t="s">
-        <v>27</v>
-      </c>
-      <c r="G70" t="s">
-        <v>42</v>
-      </c>
-      <c r="H70" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" t="s">
-        <v>752</v>
-      </c>
-      <c r="B71" s="19">
-        <v>32993</v>
-      </c>
-      <c r="C71" t="s">
-        <v>190</v>
-      </c>
-      <c r="D71" t="s">
-        <v>197</v>
-      </c>
-      <c r="E71" t="s">
-        <v>42</v>
-      </c>
-      <c r="F71" t="s">
+      <c r="F83" t="s">
         <v>41</v>
       </c>
-      <c r="G71" t="s">
+      <c r="G83" t="s">
         <v>41</v>
       </c>
-      <c r="H71" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" t="s">
-        <v>753</v>
-      </c>
-      <c r="B72" s="19">
-        <v>33639</v>
-      </c>
-      <c r="C72" t="s">
-        <v>239</v>
-      </c>
-      <c r="D72" t="s">
-        <v>244</v>
-      </c>
-      <c r="E72" t="s">
-        <v>694</v>
-      </c>
-      <c r="F72" t="s">
-        <v>42</v>
-      </c>
-      <c r="G72" t="s">
-        <v>694</v>
-      </c>
-      <c r="H72" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" t="s">
-        <v>754</v>
-      </c>
-      <c r="B73" s="19">
-        <v>41401</v>
-      </c>
-      <c r="C73" t="s">
-        <v>524</v>
-      </c>
-      <c r="D73" t="s">
-        <v>442</v>
-      </c>
-      <c r="E73" t="s">
-        <v>117</v>
-      </c>
-      <c r="F73" t="s">
-        <v>117</v>
-      </c>
-      <c r="G73" t="s">
-        <v>694</v>
-      </c>
-      <c r="H73" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" t="s">
-        <v>755</v>
-      </c>
-      <c r="B74" s="19">
-        <v>40218</v>
-      </c>
-      <c r="C74" t="s">
-        <v>569</v>
-      </c>
-      <c r="D74" t="s">
-        <v>278</v>
-      </c>
-      <c r="E74" t="s">
-        <v>42</v>
-      </c>
-      <c r="F74" t="s">
-        <v>41</v>
-      </c>
-      <c r="G74" t="s">
-        <v>41</v>
-      </c>
-      <c r="H74" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" t="s">
-        <v>756</v>
-      </c>
-      <c r="B75" s="19">
-        <v>43289</v>
-      </c>
-      <c r="C75" t="s">
-        <v>352</v>
-      </c>
-      <c r="D75" t="s">
-        <v>352</v>
-      </c>
-      <c r="E75" t="s">
-        <v>41</v>
-      </c>
-      <c r="F75" t="s">
-        <v>41</v>
-      </c>
-      <c r="G75" t="s">
-        <v>42</v>
-      </c>
-      <c r="H75" s="3">
+      <c r="H83" t="s">
+        <v>42</v>
+      </c>
+      <c r="I83" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
-      <c r="A76" t="s">
-        <v>757</v>
-      </c>
-      <c r="B76" s="19">
-        <v>38096</v>
-      </c>
-      <c r="C76" t="s">
-        <v>112</v>
-      </c>
-      <c r="D76" t="s">
-        <v>119</v>
-      </c>
-      <c r="E76" t="s">
-        <v>117</v>
-      </c>
-      <c r="F76" t="s">
-        <v>117</v>
-      </c>
-      <c r="G76" t="s">
-        <v>41</v>
-      </c>
-      <c r="H76" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" t="s">
-        <v>758</v>
-      </c>
-      <c r="B77" s="19">
-        <v>33729</v>
-      </c>
-      <c r="C77" t="s">
-        <v>460</v>
-      </c>
-      <c r="D77" t="s">
-        <v>228</v>
-      </c>
-      <c r="E77" t="s">
-        <v>27</v>
-      </c>
-      <c r="F77" t="s">
-        <v>27</v>
-      </c>
-      <c r="G77" t="s">
-        <v>42</v>
-      </c>
-      <c r="H77" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" t="s">
-        <v>759</v>
-      </c>
-      <c r="B78" s="19">
-        <v>35358</v>
-      </c>
-      <c r="C78" t="s">
-        <v>425</v>
-      </c>
-      <c r="D78" t="s">
-        <v>705</v>
-      </c>
-      <c r="E78" t="s">
-        <v>26</v>
-      </c>
-      <c r="F78" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" t="s">
-        <v>27</v>
-      </c>
-      <c r="H78" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
-      <c r="A79" t="s">
-        <v>760</v>
-      </c>
-      <c r="B79" s="19">
-        <v>33494</v>
-      </c>
-      <c r="C79" t="s">
-        <v>469</v>
-      </c>
-      <c r="D79" t="s">
-        <v>352</v>
-      </c>
-      <c r="E79" t="s">
-        <v>67</v>
-      </c>
-      <c r="F79" t="s">
-        <v>67</v>
-      </c>
-      <c r="G79" t="s">
-        <v>42</v>
-      </c>
-      <c r="H79" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80" t="s">
-        <v>761</v>
-      </c>
-      <c r="B80" s="19">
-        <v>30717</v>
-      </c>
-      <c r="C80" t="s">
-        <v>258</v>
-      </c>
-      <c r="D80" t="s">
-        <v>210</v>
-      </c>
-      <c r="E80" t="s">
-        <v>26</v>
-      </c>
-      <c r="F80" t="s">
-        <v>42</v>
-      </c>
-      <c r="G80" t="s">
-        <v>42</v>
-      </c>
-      <c r="H80" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
-      <c r="A81" t="s">
-        <v>762</v>
-      </c>
-      <c r="B81" s="19">
-        <v>31759</v>
-      </c>
-      <c r="C81" t="s">
-        <v>580</v>
-      </c>
-      <c r="D81" t="s">
-        <v>119</v>
-      </c>
-      <c r="E81" t="s">
-        <v>42</v>
-      </c>
-      <c r="F81" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82" t="s">
-        <v>763</v>
-      </c>
-      <c r="B82" s="19">
-        <v>31048</v>
-      </c>
-      <c r="C82" t="s">
-        <v>229</v>
-      </c>
-      <c r="D82" t="s">
-        <v>119</v>
-      </c>
-      <c r="E82" t="s">
-        <v>117</v>
-      </c>
-      <c r="F82" t="s">
-        <v>27</v>
-      </c>
-      <c r="G82" t="s">
-        <v>27</v>
-      </c>
-      <c r="H82" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
-      <c r="A83" t="s">
-        <v>764</v>
-      </c>
-      <c r="B83" s="19">
-        <v>31048</v>
-      </c>
-      <c r="C83" t="s">
-        <v>285</v>
-      </c>
-      <c r="D83" t="s">
-        <v>244</v>
-      </c>
-      <c r="E83" t="s">
-        <v>42</v>
-      </c>
-      <c r="F83" t="s">
-        <v>27</v>
-      </c>
-      <c r="G83" t="s">
-        <v>27</v>
-      </c>
-      <c r="H83" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>765</v>
-      </c>
-      <c r="B84" s="19">
-        <v>30327</v>
-      </c>
-      <c r="C84" t="s">
-        <v>34</v>
+        <v>737</v>
+      </c>
+      <c r="B84" t="s">
+        <v>918</v>
+      </c>
+      <c r="C84" s="19">
+        <v>25897</v>
       </c>
       <c r="D84" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E84" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="F84" t="s">
         <v>41</v>
@@ -12012,727 +12641,811 @@
       <c r="G84" t="s">
         <v>41</v>
       </c>
-      <c r="H84" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+      <c r="H84" t="s">
+        <v>26</v>
+      </c>
+      <c r="I84" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>766</v>
-      </c>
-      <c r="B85" s="19">
-        <v>25901</v>
-      </c>
-      <c r="C85" t="s">
-        <v>34</v>
+        <v>748</v>
+      </c>
+      <c r="B85" t="s">
+        <v>913</v>
+      </c>
+      <c r="C85" s="19">
+        <v>32964</v>
       </c>
       <c r="D85" t="s">
+        <v>391</v>
+      </c>
+      <c r="E85" t="s">
+        <v>119</v>
+      </c>
+      <c r="F85" t="s">
+        <v>42</v>
+      </c>
+      <c r="G85" t="s">
+        <v>27</v>
+      </c>
+      <c r="H85" t="s">
+        <v>27</v>
+      </c>
+      <c r="I85" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>756</v>
+      </c>
+      <c r="B86" t="s">
+        <v>920</v>
+      </c>
+      <c r="C86" s="19">
+        <v>43289</v>
+      </c>
+      <c r="D86" t="s">
+        <v>352</v>
+      </c>
+      <c r="E86" t="s">
+        <v>352</v>
+      </c>
+      <c r="F86" t="s">
+        <v>41</v>
+      </c>
+      <c r="G86" t="s">
+        <v>41</v>
+      </c>
+      <c r="H86" t="s">
+        <v>42</v>
+      </c>
+      <c r="I86" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>769</v>
+      </c>
+      <c r="B87" t="s">
+        <v>908</v>
+      </c>
+      <c r="C87" s="19">
+        <v>39969</v>
+      </c>
+      <c r="D87" t="s">
+        <v>323</v>
+      </c>
+      <c r="E87" t="s">
+        <v>173</v>
+      </c>
+      <c r="F87" t="s">
+        <v>42</v>
+      </c>
+      <c r="G87" t="s">
+        <v>694</v>
+      </c>
+      <c r="H87" t="s">
+        <v>694</v>
+      </c>
+      <c r="I87" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>772</v>
+      </c>
+      <c r="B88" t="s">
+        <v>923</v>
+      </c>
+      <c r="C88" s="19">
+        <v>26355</v>
+      </c>
+      <c r="D88" t="s">
+        <v>314</v>
+      </c>
+      <c r="E88" t="s">
         <v>38</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F88" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" t="s">
         <v>41</v>
       </c>
-      <c r="F85" t="s">
-        <v>41</v>
-      </c>
-      <c r="G85" t="s">
-        <v>42</v>
-      </c>
-      <c r="H85" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" t="s">
-        <v>745</v>
-      </c>
-      <c r="B86" s="19">
-        <v>34241</v>
-      </c>
-      <c r="C86" t="s">
-        <v>370</v>
-      </c>
-      <c r="D86" t="s">
-        <v>132</v>
-      </c>
-      <c r="E86" t="s">
-        <v>42</v>
-      </c>
-      <c r="F86" t="s">
-        <v>42</v>
-      </c>
-      <c r="G86" t="s">
-        <v>67</v>
-      </c>
-      <c r="H86" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87" t="s">
-        <v>767</v>
-      </c>
-      <c r="B87" s="19">
-        <v>38353</v>
-      </c>
-      <c r="C87" t="s">
-        <v>545</v>
-      </c>
-      <c r="D87" t="s">
-        <v>127</v>
-      </c>
-      <c r="E87" t="s">
-        <v>42</v>
-      </c>
-      <c r="F87" t="s">
-        <v>26</v>
-      </c>
-      <c r="G87" t="s">
+      <c r="H88" t="s">
+        <v>42</v>
+      </c>
+      <c r="I88" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>776</v>
+      </c>
+      <c r="B89" t="s">
+        <v>924</v>
+      </c>
+      <c r="C89" s="19">
+        <v>36412</v>
+      </c>
+      <c r="D89" t="s">
+        <v>169</v>
+      </c>
+      <c r="E89" t="s">
+        <v>173</v>
+      </c>
+      <c r="F89" t="s">
+        <v>42</v>
+      </c>
+      <c r="G89" t="s">
+        <v>42</v>
+      </c>
+      <c r="H89" t="s">
+        <v>775</v>
+      </c>
+      <c r="I89" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>784</v>
+      </c>
+      <c r="B90" t="s">
+        <v>915</v>
+      </c>
+      <c r="C90" s="19">
+        <v>32325</v>
+      </c>
+      <c r="D90" t="s">
+        <v>98</v>
+      </c>
+      <c r="E90" t="s">
+        <v>98</v>
+      </c>
+      <c r="F90" t="s">
+        <v>42</v>
+      </c>
+      <c r="G90" t="s">
         <v>27</v>
       </c>
-      <c r="H87" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" t="s">
-        <v>768</v>
-      </c>
-      <c r="B88" s="19">
-        <v>32675</v>
-      </c>
-      <c r="C88" t="s">
-        <v>323</v>
-      </c>
-      <c r="D88" t="s">
-        <v>173</v>
-      </c>
-      <c r="E88" t="s">
-        <v>694</v>
-      </c>
-      <c r="F88" t="s">
-        <v>42</v>
-      </c>
-      <c r="G88" t="s">
-        <v>42</v>
-      </c>
-      <c r="H88" s="3">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89" t="s">
-        <v>769</v>
-      </c>
-      <c r="B89" s="19">
-        <v>39969</v>
-      </c>
-      <c r="C89" t="s">
-        <v>323</v>
-      </c>
-      <c r="D89" t="s">
-        <v>173</v>
-      </c>
-      <c r="E89" t="s">
-        <v>42</v>
-      </c>
-      <c r="F89" t="s">
-        <v>694</v>
-      </c>
-      <c r="G89" t="s">
-        <v>694</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H90" t="s">
+        <v>27</v>
+      </c>
+      <c r="I90" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
-      <c r="A90" t="s">
-        <v>770</v>
-      </c>
-      <c r="B90" s="19">
-        <v>34108</v>
-      </c>
-      <c r="C90" t="s">
-        <v>359</v>
-      </c>
-      <c r="D90" t="s">
-        <v>197</v>
-      </c>
-      <c r="E90" t="s">
-        <v>117</v>
-      </c>
-      <c r="F90" t="s">
-        <v>67</v>
-      </c>
-      <c r="G90" t="s">
-        <v>67</v>
-      </c>
-      <c r="H90" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>771</v>
-      </c>
-      <c r="B91" s="19">
-        <v>25285</v>
-      </c>
-      <c r="C91" t="s">
-        <v>267</v>
+        <v>801</v>
+      </c>
+      <c r="B91" t="s">
+        <v>832</v>
+      </c>
+      <c r="C91" s="19">
+        <v>37575</v>
       </c>
       <c r="D91" t="s">
-        <v>127</v>
+        <v>563</v>
       </c>
       <c r="E91" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="F91" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="G91" t="s">
         <v>27</v>
       </c>
-      <c r="H91" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
+      <c r="H91" t="s">
+        <v>27</v>
+      </c>
+      <c r="I91" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>772</v>
-      </c>
-      <c r="B92" s="19">
-        <v>26355</v>
-      </c>
-      <c r="C92" t="s">
-        <v>314</v>
+        <v>802</v>
+      </c>
+      <c r="B92" t="s">
+        <v>909</v>
+      </c>
+      <c r="C92" s="19">
+        <v>36192</v>
       </c>
       <c r="D92" t="s">
-        <v>38</v>
+        <v>529</v>
       </c>
       <c r="E92" t="s">
+        <v>488</v>
+      </c>
+      <c r="F92" t="s">
+        <v>42</v>
+      </c>
+      <c r="G92" t="s">
+        <v>67</v>
+      </c>
+      <c r="H92" t="s">
+        <v>67</v>
+      </c>
+      <c r="I92" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>805</v>
+      </c>
+      <c r="B93" t="s">
+        <v>910</v>
+      </c>
+      <c r="C93" s="19">
+        <v>37257</v>
+      </c>
+      <c r="D93" t="s">
+        <v>596</v>
+      </c>
+      <c r="E93" t="s">
+        <v>197</v>
+      </c>
+      <c r="F93" t="s">
+        <v>117</v>
+      </c>
+      <c r="G93" t="s">
+        <v>117</v>
+      </c>
+      <c r="H93" t="s">
+        <v>41</v>
+      </c>
+      <c r="I93" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>809</v>
+      </c>
+      <c r="B94" t="s">
+        <v>922</v>
+      </c>
+      <c r="C94" s="19">
+        <v>36638</v>
+      </c>
+      <c r="D94" t="s">
+        <v>627</v>
+      </c>
+      <c r="E94" t="s">
+        <v>228</v>
+      </c>
+      <c r="F94" t="s">
+        <v>42</v>
+      </c>
+      <c r="G94" t="s">
         <v>26</v>
       </c>
-      <c r="F92" t="s">
+      <c r="H94" t="s">
+        <v>26</v>
+      </c>
+      <c r="I94" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>810</v>
+      </c>
+      <c r="B95" t="s">
+        <v>869</v>
+      </c>
+      <c r="C95" s="19">
+        <v>43728</v>
+      </c>
+      <c r="D95" t="s">
+        <v>632</v>
+      </c>
+      <c r="E95" t="s">
+        <v>244</v>
+      </c>
+      <c r="F95" t="s">
         <v>41</v>
       </c>
-      <c r="G92" t="s">
-        <v>42</v>
-      </c>
-      <c r="H92" s="3">
+      <c r="G95" t="s">
+        <v>27</v>
+      </c>
+      <c r="H95" t="s">
+        <v>42</v>
+      </c>
+      <c r="I95" s="20">
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
-      <c r="A93" t="s">
-        <v>773</v>
-      </c>
-      <c r="B93" s="19">
-        <v>38424</v>
-      </c>
-      <c r="C93" t="s">
-        <v>540</v>
-      </c>
-      <c r="D93" t="s">
-        <v>336</v>
-      </c>
-      <c r="E93" t="s">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>811</v>
+      </c>
+      <c r="B96" t="s">
+        <v>926</v>
+      </c>
+      <c r="C96" s="19">
+        <v>44562</v>
+      </c>
+      <c r="D96" t="s">
+        <v>636</v>
+      </c>
+      <c r="E96" t="s">
+        <v>249</v>
+      </c>
+      <c r="F96" t="s">
+        <v>42</v>
+      </c>
+      <c r="G96" t="s">
+        <v>67</v>
+      </c>
+      <c r="H96" t="s">
+        <v>67</v>
+      </c>
+      <c r="I96" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>815</v>
+      </c>
+      <c r="B97" t="s">
+        <v>925</v>
+      </c>
+      <c r="C97" s="19">
+        <v>44562</v>
+      </c>
+      <c r="D97" t="s">
+        <v>656</v>
+      </c>
+      <c r="E97" t="s">
+        <v>173</v>
+      </c>
+      <c r="F97" t="s">
+        <v>694</v>
+      </c>
+      <c r="G97" t="s">
+        <v>67</v>
+      </c>
+      <c r="H97" t="s">
+        <v>42</v>
+      </c>
+      <c r="I97" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>816</v>
+      </c>
+      <c r="B98" t="s">
+        <v>921</v>
+      </c>
+      <c r="C98" s="19">
+        <v>34520</v>
+      </c>
+      <c r="D98" t="s">
+        <v>661</v>
+      </c>
+      <c r="E98" t="s">
+        <v>202</v>
+      </c>
+      <c r="F98" t="s">
         <v>26</v>
       </c>
-      <c r="F93" t="s">
-        <v>26</v>
-      </c>
-      <c r="G93" t="s">
-        <v>42</v>
-      </c>
-      <c r="H93" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
-      <c r="A94" t="s">
-        <v>774</v>
-      </c>
-      <c r="B94" s="19">
-        <v>32598</v>
-      </c>
-      <c r="C94" t="s">
-        <v>169</v>
-      </c>
-      <c r="D94" t="s">
-        <v>173</v>
-      </c>
-      <c r="E94" t="s">
-        <v>775</v>
-      </c>
-      <c r="F94" t="s">
-        <v>775</v>
-      </c>
-      <c r="G94" t="s">
-        <v>42</v>
-      </c>
-      <c r="H94" s="3">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
-      <c r="A95" t="s">
-        <v>776</v>
-      </c>
-      <c r="B95" s="19">
-        <v>36412</v>
-      </c>
-      <c r="C95" t="s">
-        <v>169</v>
-      </c>
-      <c r="D95" t="s">
-        <v>173</v>
-      </c>
-      <c r="E95" t="s">
-        <v>42</v>
-      </c>
-      <c r="F95" t="s">
-        <v>42</v>
-      </c>
-      <c r="G95" t="s">
-        <v>775</v>
-      </c>
-      <c r="H95" s="3">
+      <c r="G98" t="s">
+        <v>42</v>
+      </c>
+      <c r="H98" t="s">
+        <v>27</v>
+      </c>
+      <c r="I98" s="20">
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
-      <c r="A96" t="s">
-        <v>777</v>
-      </c>
-      <c r="B96" s="19">
-        <v>39155</v>
-      </c>
-      <c r="C96" t="s">
-        <v>413</v>
-      </c>
-      <c r="D96" t="s">
-        <v>352</v>
-      </c>
-      <c r="E96" t="s">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>818</v>
+      </c>
+      <c r="B99" t="s">
+        <v>846</v>
+      </c>
+      <c r="C99" s="19">
+        <v>37299</v>
+      </c>
+      <c r="D99" t="s">
+        <v>503</v>
+      </c>
+      <c r="E99" t="s">
+        <v>119</v>
+      </c>
+      <c r="F99" t="s">
         <v>27</v>
-      </c>
-      <c r="F96" t="s">
-        <v>27</v>
-      </c>
-      <c r="G96" t="s">
-        <v>42</v>
-      </c>
-      <c r="H96" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" t="s">
-        <v>778</v>
-      </c>
-      <c r="B97" s="19">
-        <v>30108</v>
-      </c>
-      <c r="C97" t="s">
-        <v>425</v>
-      </c>
-      <c r="D97" t="s">
-        <v>705</v>
-      </c>
-      <c r="E97" t="s">
-        <v>27</v>
-      </c>
-      <c r="F97" t="s">
-        <v>26</v>
-      </c>
-      <c r="G97" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98" t="s">
-        <v>779</v>
-      </c>
-      <c r="B98" s="19">
-        <v>36662</v>
-      </c>
-      <c r="C98" t="s">
-        <v>397</v>
-      </c>
-      <c r="D98" t="s">
-        <v>705</v>
-      </c>
-      <c r="E98" t="s">
-        <v>117</v>
-      </c>
-      <c r="F98" t="s">
-        <v>117</v>
-      </c>
-      <c r="G98" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
-      <c r="A99" t="s">
-        <v>780</v>
-      </c>
-      <c r="B99" s="19">
-        <v>33719</v>
-      </c>
-      <c r="C99" t="s">
-        <v>284</v>
-      </c>
-      <c r="D99" t="s">
-        <v>210</v>
-      </c>
-      <c r="E99" t="s">
-        <v>42</v>
-      </c>
-      <c r="F99" t="s">
-        <v>42</v>
       </c>
       <c r="G99" t="s">
         <v>27</v>
       </c>
-      <c r="H99" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
+      <c r="H99" t="s">
+        <v>26</v>
+      </c>
+      <c r="I99" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>781</v>
-      </c>
-      <c r="B100" s="19">
-        <v>39396</v>
-      </c>
-      <c r="C100" t="s">
-        <v>284</v>
+        <v>679</v>
+      </c>
+      <c r="B100" t="s">
+        <v>830</v>
+      </c>
+      <c r="C100" s="19">
+        <v>42736</v>
       </c>
       <c r="D100" t="s">
-        <v>210</v>
+        <v>329</v>
       </c>
       <c r="E100" t="s">
+        <v>336</v>
+      </c>
+      <c r="F100" t="s">
+        <v>27</v>
+      </c>
+      <c r="G100" t="s">
+        <v>27</v>
+      </c>
+      <c r="H100" t="s">
+        <v>42</v>
+      </c>
+      <c r="I100" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>723</v>
+      </c>
+      <c r="B101" t="s">
+        <v>927</v>
+      </c>
+      <c r="C101" s="19">
+        <v>35125</v>
+      </c>
+      <c r="D101" t="s">
+        <v>158</v>
+      </c>
+      <c r="E101" t="s">
+        <v>132</v>
+      </c>
+      <c r="F101" t="s">
+        <v>42</v>
+      </c>
+      <c r="G101" t="s">
+        <v>41</v>
+      </c>
+      <c r="H101" t="s">
+        <v>41</v>
+      </c>
+      <c r="I101" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>725</v>
+      </c>
+      <c r="B102" t="s">
+        <v>919</v>
+      </c>
+      <c r="C102" s="19">
+        <v>39640</v>
+      </c>
+      <c r="D102" t="s">
+        <v>250</v>
+      </c>
+      <c r="E102" t="s">
+        <v>257</v>
+      </c>
+      <c r="F102" t="s">
         <v>26</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G102" t="s">
+        <v>42</v>
+      </c>
+      <c r="H102" t="s">
+        <v>117</v>
+      </c>
+      <c r="I102" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>681</v>
+      </c>
+      <c r="B103" t="s">
+        <v>838</v>
+      </c>
+      <c r="C103" s="19">
+        <v>25934</v>
+      </c>
+      <c r="D103" t="s">
+        <v>551</v>
+      </c>
+      <c r="E103" t="s">
+        <v>442</v>
+      </c>
+      <c r="F103" t="s">
         <v>26</v>
       </c>
-      <c r="G100" t="s">
-        <v>42</v>
-      </c>
-      <c r="H100" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
-      <c r="A101" t="s">
-        <v>782</v>
-      </c>
-      <c r="B101" s="19">
-        <v>36820</v>
-      </c>
-      <c r="C101" t="s">
-        <v>513</v>
-      </c>
-      <c r="D101" t="s">
-        <v>298</v>
-      </c>
-      <c r="E101" t="s">
-        <v>42</v>
-      </c>
-      <c r="F101" t="s">
-        <v>67</v>
-      </c>
-      <c r="G101" t="s">
-        <v>67</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="G103" t="s">
+        <v>42</v>
+      </c>
+      <c r="H103" t="s">
+        <v>42</v>
+      </c>
+      <c r="I103" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
-      <c r="A102" t="s">
-        <v>783</v>
-      </c>
-      <c r="B102" s="19">
-        <v>25472</v>
-      </c>
-      <c r="C102" t="s">
-        <v>98</v>
-      </c>
-      <c r="D102" t="s">
-        <v>98</v>
-      </c>
-      <c r="E102" t="s">
-        <v>42</v>
-      </c>
-      <c r="F102" t="s">
-        <v>42</v>
-      </c>
-      <c r="G102" t="s">
-        <v>27</v>
-      </c>
-      <c r="H102" s="3">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
-      <c r="A103" t="s">
-        <v>784</v>
-      </c>
-      <c r="B103" s="19">
-        <v>32325</v>
-      </c>
-      <c r="C103" t="s">
-        <v>98</v>
-      </c>
-      <c r="D103" t="s">
-        <v>98</v>
-      </c>
-      <c r="E103" t="s">
-        <v>42</v>
-      </c>
-      <c r="F103" t="s">
-        <v>27</v>
-      </c>
-      <c r="G103" t="s">
-        <v>27</v>
-      </c>
-      <c r="H103" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>785</v>
-      </c>
-      <c r="B104" s="19">
-        <v>38493</v>
-      </c>
-      <c r="C104" t="s">
-        <v>291</v>
+        <v>682</v>
+      </c>
+      <c r="B104" t="s">
+        <v>839</v>
+      </c>
+      <c r="C104" s="19">
+        <v>37510</v>
       </c>
       <c r="D104" t="s">
-        <v>298</v>
+        <v>218</v>
       </c>
       <c r="E104" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="F104" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G104" t="s">
         <v>27</v>
       </c>
-      <c r="H104" s="3">
+      <c r="H104" t="s">
+        <v>42</v>
+      </c>
+      <c r="I104" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>786</v>
-      </c>
-      <c r="B105" s="19">
-        <v>34772</v>
-      </c>
-      <c r="C105" t="s">
-        <v>498</v>
+        <v>685</v>
+      </c>
+      <c r="B105" t="s">
+        <v>843</v>
+      </c>
+      <c r="C105" s="19">
+        <v>37157</v>
       </c>
       <c r="D105" t="s">
-        <v>298</v>
+        <v>559</v>
       </c>
       <c r="E105" t="s">
-        <v>67</v>
+        <v>442</v>
       </c>
       <c r="F105" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="G105" t="s">
-        <v>42</v>
-      </c>
-      <c r="H105" s="3">
+        <v>27</v>
+      </c>
+      <c r="H105" t="s">
+        <v>27</v>
+      </c>
+      <c r="I105" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>787</v>
-      </c>
-      <c r="B106" s="19">
-        <v>26497</v>
-      </c>
-      <c r="C106" t="s">
-        <v>38</v>
+        <v>687</v>
+      </c>
+      <c r="B106" t="s">
+        <v>845</v>
+      </c>
+      <c r="C106" s="19">
+        <v>44562</v>
       </c>
       <c r="D106" t="s">
-        <v>38</v>
+        <v>273</v>
       </c>
       <c r="E106" t="s">
-        <v>42</v>
+        <v>278</v>
       </c>
       <c r="F106" t="s">
         <v>42</v>
       </c>
       <c r="G106" t="s">
+        <v>27</v>
+      </c>
+      <c r="H106" t="s">
+        <v>27</v>
+      </c>
+      <c r="I106" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>689</v>
+      </c>
+      <c r="B107" t="s">
+        <v>851</v>
+      </c>
+      <c r="C107" s="19">
+        <v>33865</v>
+      </c>
+      <c r="D107" t="s">
+        <v>128</v>
+      </c>
+      <c r="E107" t="s">
+        <v>132</v>
+      </c>
+      <c r="F107" t="s">
+        <v>27</v>
+      </c>
+      <c r="G107" t="s">
+        <v>27</v>
+      </c>
+      <c r="H107" t="s">
         <v>26</v>
       </c>
-      <c r="H106" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
-      <c r="A107" t="s">
-        <v>788</v>
-      </c>
-      <c r="B107" s="19">
-        <v>30848</v>
-      </c>
-      <c r="C107" t="s">
-        <v>38</v>
-      </c>
-      <c r="D107" t="s">
-        <v>38</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="I107" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>700</v>
+      </c>
+      <c r="B108" t="s">
+        <v>860</v>
+      </c>
+      <c r="C108" s="19">
+        <v>38564</v>
+      </c>
+      <c r="D108" t="s">
+        <v>534</v>
+      </c>
+      <c r="E108" t="s">
+        <v>336</v>
+      </c>
+      <c r="F108" t="s">
+        <v>42</v>
+      </c>
+      <c r="G108" t="s">
+        <v>41</v>
+      </c>
+      <c r="H108" t="s">
         <v>26</v>
       </c>
-      <c r="F107" t="s">
-        <v>26</v>
-      </c>
-      <c r="G107" t="s">
-        <v>42</v>
-      </c>
-      <c r="H107" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
-      <c r="A108" t="s">
-        <v>789</v>
-      </c>
-      <c r="B108" s="19">
-        <v>34189</v>
-      </c>
-      <c r="C108" t="s">
-        <v>369</v>
-      </c>
-      <c r="D108" t="s">
-        <v>369</v>
-      </c>
-      <c r="E108" t="s">
-        <v>26</v>
-      </c>
-      <c r="F108" t="s">
-        <v>42</v>
-      </c>
-      <c r="G108" t="s">
-        <v>42</v>
-      </c>
-      <c r="H108" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8">
+      <c r="I108" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>790</v>
-      </c>
-      <c r="B109" s="19">
-        <v>34974</v>
-      </c>
-      <c r="C109" t="s">
-        <v>419</v>
+        <v>707</v>
+      </c>
+      <c r="B109" t="s">
+        <v>863</v>
+      </c>
+      <c r="C109" s="19">
+        <v>32489</v>
       </c>
       <c r="D109" t="s">
-        <v>306</v>
+        <v>120</v>
       </c>
       <c r="E109" t="s">
+        <v>127</v>
+      </c>
+      <c r="F109" t="s">
+        <v>708</v>
+      </c>
+      <c r="G109" t="s">
+        <v>42</v>
+      </c>
+      <c r="H109" t="s">
+        <v>27</v>
+      </c>
+      <c r="I109" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>715</v>
+      </c>
+      <c r="B110" t="s">
+        <v>928</v>
+      </c>
+      <c r="C110" s="19">
+        <v>43240</v>
+      </c>
+      <c r="D110" t="s">
+        <v>185</v>
+      </c>
+      <c r="E110" t="s">
+        <v>178</v>
+      </c>
+      <c r="F110" t="s">
+        <v>42</v>
+      </c>
+      <c r="G110" t="s">
+        <v>27</v>
+      </c>
+      <c r="H110" t="s">
+        <v>27</v>
+      </c>
+      <c r="I110" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>731</v>
+      </c>
+      <c r="B111" t="s">
+        <v>831</v>
+      </c>
+      <c r="C111" s="19">
+        <v>40596</v>
+      </c>
+      <c r="D111" t="s">
+        <v>223</v>
+      </c>
+      <c r="E111" t="s">
+        <v>228</v>
+      </c>
+      <c r="F111" t="s">
+        <v>117</v>
+      </c>
+      <c r="G111" t="s">
         <v>41</v>
       </c>
-      <c r="F109" t="s">
-        <v>42</v>
-      </c>
-      <c r="G109" t="s">
-        <v>42</v>
-      </c>
-      <c r="H109" s="3">
+      <c r="H111" t="s">
+        <v>42</v>
+      </c>
+      <c r="I111" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
-      <c r="A110" t="s">
-        <v>791</v>
-      </c>
-      <c r="B110" s="19">
-        <v>34990</v>
-      </c>
-      <c r="C110" t="s">
-        <v>206</v>
-      </c>
-      <c r="D110" t="s">
-        <v>210</v>
-      </c>
-      <c r="E110" t="s">
-        <v>117</v>
-      </c>
-      <c r="F110" t="s">
-        <v>117</v>
-      </c>
-      <c r="G110" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
-      <c r="A111" t="s">
-        <v>792</v>
-      </c>
-      <c r="B111" s="19">
-        <v>32440</v>
-      </c>
-      <c r="C111" t="s">
-        <v>206</v>
-      </c>
-      <c r="D111" t="s">
-        <v>210</v>
-      </c>
-      <c r="E111" t="s">
-        <v>26</v>
-      </c>
-      <c r="F111" t="s">
-        <v>27</v>
-      </c>
-      <c r="G111" t="s">
-        <v>27</v>
-      </c>
-      <c r="H111" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>793</v>
-      </c>
-      <c r="B112" s="19">
-        <v>37238</v>
-      </c>
-      <c r="C112" t="s">
-        <v>376</v>
+        <v>732</v>
+      </c>
+      <c r="B112" t="s">
+        <v>378</v>
+      </c>
+      <c r="C112" s="19">
+        <v>33181</v>
       </c>
       <c r="D112" t="s">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="E112" t="s">
-        <v>42</v>
+        <v>178</v>
       </c>
       <c r="F112" t="s">
         <v>42</v>
@@ -12740,720 +13453,799 @@
       <c r="G112" t="s">
         <v>27</v>
       </c>
-      <c r="H112" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
+      <c r="H112" t="s">
+        <v>26</v>
+      </c>
+      <c r="I112" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>794</v>
-      </c>
-      <c r="B113" s="19">
-        <v>33384</v>
-      </c>
-      <c r="C113" t="s">
-        <v>575</v>
+        <v>742</v>
+      </c>
+      <c r="B113" t="s">
+        <v>872</v>
+      </c>
+      <c r="C113" s="19">
+        <v>39938</v>
       </c>
       <c r="D113" t="s">
+        <v>554</v>
+      </c>
+      <c r="E113" t="s">
+        <v>442</v>
+      </c>
+      <c r="F113" t="s">
+        <v>694</v>
+      </c>
+      <c r="G113" t="s">
+        <v>42</v>
+      </c>
+      <c r="H113" t="s">
+        <v>42</v>
+      </c>
+      <c r="I113" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>754</v>
+      </c>
+      <c r="B114" t="s">
+        <v>830</v>
+      </c>
+      <c r="C114" s="19">
+        <v>41401</v>
+      </c>
+      <c r="D114" t="s">
+        <v>524</v>
+      </c>
+      <c r="E114" t="s">
+        <v>442</v>
+      </c>
+      <c r="F114" t="s">
+        <v>117</v>
+      </c>
+      <c r="G114" t="s">
+        <v>117</v>
+      </c>
+      <c r="H114" t="s">
+        <v>694</v>
+      </c>
+      <c r="I114" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>755</v>
+      </c>
+      <c r="B115" t="s">
+        <v>836</v>
+      </c>
+      <c r="C115" s="19">
+        <v>40218</v>
+      </c>
+      <c r="D115" t="s">
+        <v>569</v>
+      </c>
+      <c r="E115" t="s">
         <v>278</v>
       </c>
-      <c r="E113" t="s">
-        <v>694</v>
-      </c>
-      <c r="F113" t="s">
-        <v>42</v>
-      </c>
-      <c r="G113" t="s">
-        <v>42</v>
-      </c>
-      <c r="H113" s="3">
+      <c r="F115" t="s">
+        <v>42</v>
+      </c>
+      <c r="G115" t="s">
+        <v>41</v>
+      </c>
+      <c r="H115" t="s">
+        <v>41</v>
+      </c>
+      <c r="I115" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
-      <c r="A114" t="s">
-        <v>795</v>
-      </c>
-      <c r="B114" s="19">
-        <v>25618</v>
-      </c>
-      <c r="C114" t="s">
-        <v>136</v>
-      </c>
-      <c r="D114" t="s">
-        <v>23</v>
-      </c>
-      <c r="E114" t="s">
-        <v>42</v>
-      </c>
-      <c r="F114" t="s">
-        <v>42</v>
-      </c>
-      <c r="G114" t="s">
-        <v>27</v>
-      </c>
-      <c r="H114" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="A115" t="s">
-        <v>796</v>
-      </c>
-      <c r="B115" s="19">
-        <v>38759</v>
-      </c>
-      <c r="C115" t="s">
-        <v>136</v>
-      </c>
-      <c r="D115" t="s">
-        <v>23</v>
-      </c>
-      <c r="E115" t="s">
-        <v>27</v>
-      </c>
-      <c r="F115" t="s">
-        <v>42</v>
-      </c>
-      <c r="G115" t="s">
-        <v>42</v>
-      </c>
-      <c r="H115" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>797</v>
-      </c>
-      <c r="B116" s="19">
-        <v>34502</v>
-      </c>
-      <c r="C116" t="s">
-        <v>263</v>
+        <v>757</v>
+      </c>
+      <c r="B116" t="s">
+        <v>930</v>
+      </c>
+      <c r="C116" s="19">
+        <v>38096</v>
       </c>
       <c r="D116" t="s">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="E116" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="F116" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="G116" t="s">
-        <v>26</v>
-      </c>
-      <c r="H116" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
+        <v>117</v>
+      </c>
+      <c r="H116" t="s">
+        <v>41</v>
+      </c>
+      <c r="I116" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>798</v>
-      </c>
-      <c r="B117" s="19">
-        <v>35723</v>
-      </c>
-      <c r="C117" t="s">
-        <v>164</v>
+        <v>758</v>
+      </c>
+      <c r="B117" t="s">
+        <v>931</v>
+      </c>
+      <c r="C117" s="19">
+        <v>33729</v>
       </c>
       <c r="D117" t="s">
-        <v>60</v>
+        <v>460</v>
       </c>
       <c r="E117" t="s">
-        <v>42</v>
+        <v>228</v>
       </c>
       <c r="F117" t="s">
         <v>27</v>
       </c>
       <c r="G117" t="s">
-        <v>26</v>
-      </c>
-      <c r="H117" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="H117" t="s">
+        <v>42</v>
+      </c>
+      <c r="I117" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>799</v>
-      </c>
-      <c r="B118" s="19">
-        <v>39448</v>
-      </c>
-      <c r="C118" t="s">
-        <v>164</v>
+        <v>762</v>
+      </c>
+      <c r="B118" t="s">
+        <v>933</v>
+      </c>
+      <c r="C118" s="19">
+        <v>31759</v>
       </c>
       <c r="D118" t="s">
-        <v>60</v>
+        <v>580</v>
       </c>
       <c r="E118" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
       <c r="F118" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="G118" t="s">
         <v>26</v>
       </c>
-      <c r="H118" s="3">
+      <c r="H118" t="s">
+        <v>26</v>
+      </c>
+      <c r="I118" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>800</v>
-      </c>
-      <c r="B119" s="19">
-        <v>32796</v>
-      </c>
-      <c r="C119" t="s">
-        <v>436</v>
+        <v>763</v>
+      </c>
+      <c r="B119" t="s">
+        <v>934</v>
+      </c>
+      <c r="C119" s="19">
+        <v>31048</v>
       </c>
       <c r="D119" t="s">
-        <v>442</v>
+        <v>229</v>
       </c>
       <c r="E119" t="s">
+        <v>119</v>
+      </c>
+      <c r="F119" t="s">
         <v>117</v>
-      </c>
-      <c r="F119" t="s">
-        <v>27</v>
       </c>
       <c r="G119" t="s">
         <v>27</v>
       </c>
-      <c r="H119" s="3">
+      <c r="H119" t="s">
+        <v>27</v>
+      </c>
+      <c r="I119" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>801</v>
-      </c>
-      <c r="B120" s="19">
-        <v>37575</v>
-      </c>
-      <c r="C120" t="s">
-        <v>563</v>
+        <v>767</v>
+      </c>
+      <c r="B120" t="s">
+        <v>932</v>
+      </c>
+      <c r="C120" s="19">
+        <v>38353</v>
       </c>
       <c r="D120" t="s">
-        <v>119</v>
+        <v>545</v>
       </c>
       <c r="E120" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="F120" t="s">
+        <v>42</v>
+      </c>
+      <c r="G120" t="s">
+        <v>26</v>
+      </c>
+      <c r="H120" t="s">
         <v>27</v>
       </c>
-      <c r="G120" t="s">
+      <c r="I120" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>773</v>
+      </c>
+      <c r="B121" t="s">
+        <v>935</v>
+      </c>
+      <c r="C121" s="19">
+        <v>38424</v>
+      </c>
+      <c r="D121" t="s">
+        <v>540</v>
+      </c>
+      <c r="E121" t="s">
+        <v>336</v>
+      </c>
+      <c r="F121" t="s">
+        <v>26</v>
+      </c>
+      <c r="G121" t="s">
+        <v>26</v>
+      </c>
+      <c r="H121" t="s">
+        <v>42</v>
+      </c>
+      <c r="I121" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>777</v>
+      </c>
+      <c r="C122" s="19">
+        <v>39155</v>
+      </c>
+      <c r="D122" t="s">
+        <v>413</v>
+      </c>
+      <c r="E122" t="s">
+        <v>352</v>
+      </c>
+      <c r="F122" t="s">
         <v>27</v>
       </c>
-      <c r="H120" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8">
-      <c r="A121" t="s">
-        <v>802</v>
-      </c>
-      <c r="B121" s="19">
-        <v>36192</v>
-      </c>
-      <c r="C121" t="s">
-        <v>529</v>
-      </c>
-      <c r="D121" t="s">
-        <v>488</v>
-      </c>
-      <c r="E121" t="s">
-        <v>42</v>
-      </c>
-      <c r="F121" t="s">
+      <c r="G122" t="s">
+        <v>27</v>
+      </c>
+      <c r="H122" t="s">
+        <v>42</v>
+      </c>
+      <c r="I122" s="21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>778</v>
+      </c>
+      <c r="B123" t="s">
+        <v>936</v>
+      </c>
+      <c r="C123" s="19">
+        <v>30108</v>
+      </c>
+      <c r="D123" t="s">
+        <v>425</v>
+      </c>
+      <c r="E123" t="s">
+        <v>705</v>
+      </c>
+      <c r="F123" t="s">
+        <v>27</v>
+      </c>
+      <c r="G123" t="s">
+        <v>26</v>
+      </c>
+      <c r="H123" t="s">
+        <v>26</v>
+      </c>
+      <c r="I123" s="21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>782</v>
+      </c>
+      <c r="B124" t="s">
+        <v>905</v>
+      </c>
+      <c r="C124" s="19">
+        <v>36820</v>
+      </c>
+      <c r="D124" t="s">
+        <v>513</v>
+      </c>
+      <c r="E124" t="s">
+        <v>298</v>
+      </c>
+      <c r="F124" t="s">
+        <v>42</v>
+      </c>
+      <c r="G124" t="s">
         <v>67</v>
       </c>
-      <c r="G121" t="s">
+      <c r="H124" t="s">
         <v>67</v>
       </c>
-      <c r="H121" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8">
-      <c r="A122" t="s">
-        <v>803</v>
-      </c>
-      <c r="B122" s="19">
-        <v>42005</v>
-      </c>
-      <c r="C122" t="s">
-        <v>587</v>
-      </c>
-      <c r="D122" t="s">
-        <v>705</v>
-      </c>
-      <c r="E122" t="s">
-        <v>26</v>
-      </c>
-      <c r="F122" t="s">
-        <v>26</v>
-      </c>
-      <c r="G122" t="s">
-        <v>42</v>
-      </c>
-      <c r="H122">
+      <c r="I124" s="21">
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
-      <c r="A123" t="s">
-        <v>804</v>
-      </c>
-      <c r="B123" s="19">
-        <v>42005</v>
-      </c>
-      <c r="C123" t="s">
-        <v>592</v>
-      </c>
-      <c r="D123" t="s">
-        <v>409</v>
-      </c>
-      <c r="E123" t="s">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>785</v>
+      </c>
+      <c r="B125" t="s">
+        <v>929</v>
+      </c>
+      <c r="C125" s="19">
+        <v>38493</v>
+      </c>
+      <c r="D125" t="s">
+        <v>291</v>
+      </c>
+      <c r="E125" t="s">
+        <v>298</v>
+      </c>
+      <c r="F125" t="s">
+        <v>117</v>
+      </c>
+      <c r="G125" t="s">
         <v>27</v>
       </c>
-      <c r="F123" t="s">
-        <v>42</v>
-      </c>
-      <c r="G123" t="s">
-        <v>42</v>
-      </c>
-      <c r="H123">
+      <c r="H125" t="s">
+        <v>27</v>
+      </c>
+      <c r="I125" s="21">
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
-      <c r="A124" t="s">
-        <v>805</v>
-      </c>
-      <c r="B124" s="19">
-        <v>37257</v>
-      </c>
-      <c r="C124" t="s">
-        <v>596</v>
-      </c>
-      <c r="D124" t="s">
-        <v>197</v>
-      </c>
-      <c r="E124" t="s">
-        <v>117</v>
-      </c>
-      <c r="F124" t="s">
-        <v>117</v>
-      </c>
-      <c r="G124" t="s">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>786</v>
+      </c>
+      <c r="B126" t="s">
+        <v>865</v>
+      </c>
+      <c r="C126" s="19">
+        <v>34772</v>
+      </c>
+      <c r="D126" t="s">
+        <v>498</v>
+      </c>
+      <c r="E126" t="s">
+        <v>298</v>
+      </c>
+      <c r="F126" t="s">
+        <v>67</v>
+      </c>
+      <c r="G126" t="s">
+        <v>67</v>
+      </c>
+      <c r="H126" t="s">
+        <v>42</v>
+      </c>
+      <c r="I126" s="21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>790</v>
+      </c>
+      <c r="B127" t="s">
+        <v>905</v>
+      </c>
+      <c r="C127" s="19">
+        <v>34974</v>
+      </c>
+      <c r="D127" t="s">
+        <v>419</v>
+      </c>
+      <c r="E127" t="s">
+        <v>306</v>
+      </c>
+      <c r="F127" t="s">
         <v>41</v>
       </c>
-      <c r="H124">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8">
-      <c r="A125" t="s">
-        <v>806</v>
-      </c>
-      <c r="B125" s="19">
-        <v>39668</v>
-      </c>
-      <c r="C125" t="s">
-        <v>602</v>
-      </c>
-      <c r="D125" t="s">
-        <v>108</v>
-      </c>
-      <c r="E125" t="s">
+      <c r="G127" t="s">
+        <v>42</v>
+      </c>
+      <c r="H127" t="s">
+        <v>42</v>
+      </c>
+      <c r="I127" s="21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>794</v>
+      </c>
+      <c r="B128" t="s">
+        <v>938</v>
+      </c>
+      <c r="C128" s="19">
+        <v>33384</v>
+      </c>
+      <c r="D128" t="s">
+        <v>575</v>
+      </c>
+      <c r="E128" t="s">
+        <v>278</v>
+      </c>
+      <c r="F128" t="s">
         <v>694</v>
       </c>
-      <c r="F125" t="s">
-        <v>42</v>
-      </c>
-      <c r="G125" t="s">
-        <v>42</v>
-      </c>
-      <c r="H125">
+      <c r="G128" t="s">
+        <v>42</v>
+      </c>
+      <c r="H128" t="s">
+        <v>42</v>
+      </c>
+      <c r="I128" s="21">
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
-      <c r="A126" t="s">
-        <v>807</v>
-      </c>
-      <c r="B126" s="19">
-        <v>36568</v>
-      </c>
-      <c r="C126" t="s">
-        <v>614</v>
-      </c>
-      <c r="D126" t="s">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>799</v>
+      </c>
+      <c r="B129" t="s">
+        <v>939</v>
+      </c>
+      <c r="C129" s="19">
+        <v>39448</v>
+      </c>
+      <c r="D129" t="s">
+        <v>164</v>
+      </c>
+      <c r="E129" t="s">
         <v>60</v>
-      </c>
-      <c r="E126" t="s">
-        <v>42</v>
-      </c>
-      <c r="F126" t="s">
-        <v>41</v>
-      </c>
-      <c r="G126" t="s">
-        <v>26</v>
-      </c>
-      <c r="H126">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8">
-      <c r="A127" t="s">
-        <v>808</v>
-      </c>
-      <c r="B127" s="19">
-        <v>38869</v>
-      </c>
-      <c r="C127" t="s">
-        <v>621</v>
-      </c>
-      <c r="D127" t="s">
-        <v>173</v>
-      </c>
-      <c r="E127" t="s">
-        <v>41</v>
-      </c>
-      <c r="F127" t="s">
-        <v>42</v>
-      </c>
-      <c r="G127" t="s">
-        <v>42</v>
-      </c>
-      <c r="H127">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8">
-      <c r="A128" t="s">
-        <v>809</v>
-      </c>
-      <c r="B128" s="19">
-        <v>36638</v>
-      </c>
-      <c r="C128" t="s">
-        <v>627</v>
-      </c>
-      <c r="D128" t="s">
-        <v>228</v>
-      </c>
-      <c r="E128" t="s">
-        <v>42</v>
-      </c>
-      <c r="F128" t="s">
-        <v>26</v>
-      </c>
-      <c r="G128" t="s">
-        <v>26</v>
-      </c>
-      <c r="H128">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8">
-      <c r="A129" t="s">
-        <v>810</v>
-      </c>
-      <c r="B129" s="19">
-        <v>43728</v>
-      </c>
-      <c r="C129" t="s">
-        <v>632</v>
-      </c>
-      <c r="D129" t="s">
-        <v>244</v>
-      </c>
-      <c r="E129" t="s">
-        <v>41</v>
       </c>
       <c r="F129" t="s">
         <v>27</v>
       </c>
       <c r="G129" t="s">
-        <v>42</v>
-      </c>
-      <c r="H129">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="H129" t="s">
+        <v>26</v>
+      </c>
+      <c r="I129" s="21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>811</v>
-      </c>
-      <c r="B130" s="19">
-        <v>44562</v>
-      </c>
-      <c r="C130" t="s">
-        <v>636</v>
+        <v>800</v>
+      </c>
+      <c r="B130" t="s">
+        <v>940</v>
+      </c>
+      <c r="C130" s="19">
+        <v>32796</v>
       </c>
       <c r="D130" t="s">
-        <v>249</v>
+        <v>436</v>
       </c>
       <c r="E130" t="s">
-        <v>42</v>
+        <v>442</v>
       </c>
       <c r="F130" t="s">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="G130" t="s">
-        <v>67</v>
-      </c>
-      <c r="H130">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="H130" t="s">
+        <v>27</v>
+      </c>
+      <c r="I130" s="21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>812</v>
-      </c>
-      <c r="B131" s="19">
-        <v>35836</v>
-      </c>
-      <c r="C131" t="s">
-        <v>641</v>
+        <v>803</v>
+      </c>
+      <c r="B131" t="s">
+        <v>941</v>
+      </c>
+      <c r="C131" s="19">
+        <v>42005</v>
       </c>
       <c r="D131" t="s">
-        <v>369</v>
+        <v>587</v>
       </c>
       <c r="E131" t="s">
-        <v>67</v>
+        <v>705</v>
       </c>
       <c r="F131" t="s">
         <v>26</v>
       </c>
       <c r="G131" t="s">
-        <v>42</v>
-      </c>
-      <c r="H131">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="H131" t="s">
+        <v>42</v>
+      </c>
+      <c r="I131">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>813</v>
-      </c>
-      <c r="B132" s="19">
-        <v>38431</v>
-      </c>
-      <c r="C132" t="s">
-        <v>647</v>
+        <v>804</v>
+      </c>
+      <c r="B132" t="s">
+        <v>944</v>
+      </c>
+      <c r="C132" s="19">
+        <v>42005</v>
       </c>
       <c r="D132" t="s">
-        <v>488</v>
+        <v>592</v>
       </c>
       <c r="E132" t="s">
-        <v>42</v>
+        <v>409</v>
       </c>
       <c r="F132" t="s">
+        <v>27</v>
+      </c>
+      <c r="G132" t="s">
+        <v>42</v>
+      </c>
+      <c r="H132" t="s">
+        <v>42</v>
+      </c>
+      <c r="I132">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>806</v>
+      </c>
+      <c r="B133" t="s">
+        <v>945</v>
+      </c>
+      <c r="C133" s="19">
+        <v>39668</v>
+      </c>
+      <c r="D133" t="s">
+        <v>602</v>
+      </c>
+      <c r="E133" t="s">
+        <v>108</v>
+      </c>
+      <c r="F133" t="s">
+        <v>694</v>
+      </c>
+      <c r="G133" t="s">
+        <v>42</v>
+      </c>
+      <c r="H133" t="s">
+        <v>42</v>
+      </c>
+      <c r="I133">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>807</v>
+      </c>
+      <c r="B134" t="s">
+        <v>937</v>
+      </c>
+      <c r="C134" s="19">
+        <v>36568</v>
+      </c>
+      <c r="D134" t="s">
+        <v>614</v>
+      </c>
+      <c r="E134" t="s">
+        <v>60</v>
+      </c>
+      <c r="F134" t="s">
+        <v>42</v>
+      </c>
+      <c r="G134" t="s">
         <v>41</v>
       </c>
-      <c r="G132" t="s">
+      <c r="H134" t="s">
         <v>26</v>
       </c>
-      <c r="H132">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
-      <c r="A133" t="s">
+      <c r="I134">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>808</v>
+      </c>
+      <c r="B135" t="s">
+        <v>942</v>
+      </c>
+      <c r="C135" s="19">
+        <v>38869</v>
+      </c>
+      <c r="D135" t="s">
+        <v>621</v>
+      </c>
+      <c r="E135" t="s">
+        <v>173</v>
+      </c>
+      <c r="F135" t="s">
+        <v>41</v>
+      </c>
+      <c r="G135" t="s">
+        <v>42</v>
+      </c>
+      <c r="H135" t="s">
+        <v>42</v>
+      </c>
+      <c r="I135">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
         <v>814</v>
       </c>
-      <c r="B133" s="19">
+      <c r="B136" t="s">
+        <v>946</v>
+      </c>
+      <c r="C136" s="19">
         <v>42748</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D136" t="s">
         <v>652</v>
       </c>
-      <c r="D133" t="s">
+      <c r="E136" t="s">
         <v>454</v>
       </c>
-      <c r="E133" t="s">
+      <c r="F136" t="s">
         <v>694</v>
       </c>
-      <c r="F133" t="s">
-        <v>42</v>
-      </c>
-      <c r="G133" t="s">
-        <v>42</v>
-      </c>
-      <c r="H133">
+      <c r="G136" t="s">
+        <v>42</v>
+      </c>
+      <c r="H136" t="s">
+        <v>42</v>
+      </c>
+      <c r="I136">
         <v>20</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
-      <c r="A134" t="s">
-        <v>815</v>
-      </c>
-      <c r="B134" s="19">
-        <v>44562</v>
-      </c>
-      <c r="C134" t="s">
-        <v>656</v>
-      </c>
-      <c r="D134" t="s">
-        <v>173</v>
-      </c>
-      <c r="E134" t="s">
-        <v>694</v>
-      </c>
-      <c r="F134" t="s">
-        <v>67</v>
-      </c>
-      <c r="G134" t="s">
-        <v>42</v>
-      </c>
-      <c r="H134">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8">
-      <c r="A135" t="s">
-        <v>816</v>
-      </c>
-      <c r="B135" s="19">
-        <v>34520</v>
-      </c>
-      <c r="C135" t="s">
-        <v>661</v>
-      </c>
-      <c r="D135" t="s">
-        <v>202</v>
-      </c>
-      <c r="E135" t="s">
-        <v>26</v>
-      </c>
-      <c r="F135" t="s">
-        <v>42</v>
-      </c>
-      <c r="G135" t="s">
-        <v>27</v>
-      </c>
-      <c r="H135">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8">
-      <c r="A136" t="s">
-        <v>817</v>
-      </c>
-      <c r="B136" s="19">
-        <v>37080</v>
-      </c>
-      <c r="C136" t="s">
-        <v>607</v>
-      </c>
-      <c r="D136" t="s">
-        <v>705</v>
-      </c>
-      <c r="E136" t="s">
-        <v>42</v>
-      </c>
-      <c r="F136" t="s">
-        <v>42</v>
-      </c>
-      <c r="G136" t="s">
-        <v>27</v>
-      </c>
-      <c r="H136">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>818</v>
-      </c>
-      <c r="B137" s="19">
-        <v>37299</v>
-      </c>
-      <c r="C137" t="s">
-        <v>503</v>
+        <v>819</v>
+      </c>
+      <c r="B137" t="s">
+        <v>943</v>
+      </c>
+      <c r="C137" s="19">
+        <v>37318</v>
       </c>
       <c r="D137" t="s">
-        <v>119</v>
+        <v>509</v>
       </c>
       <c r="E137" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="F137" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G137" t="s">
         <v>26</v>
       </c>
-      <c r="H137">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8">
+      <c r="H137" t="s">
+        <v>42</v>
+      </c>
+      <c r="I137">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>819</v>
-      </c>
-      <c r="B138" s="19">
-        <v>37318</v>
-      </c>
-      <c r="C138" t="s">
-        <v>509</v>
+        <v>820</v>
+      </c>
+      <c r="B138" t="s">
+        <v>947</v>
+      </c>
+      <c r="C138" s="19">
+        <v>43466</v>
       </c>
       <c r="D138" t="s">
-        <v>98</v>
+        <v>410</v>
       </c>
       <c r="E138" t="s">
+        <v>178</v>
+      </c>
+      <c r="F138" t="s">
         <v>41</v>
       </c>
-      <c r="F138" t="s">
-        <v>26</v>
-      </c>
       <c r="G138" t="s">
-        <v>42</v>
-      </c>
-      <c r="H138">
+        <v>41</v>
+      </c>
+      <c r="H138" t="s">
+        <v>42</v>
+      </c>
+      <c r="I138">
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>820</v>
-      </c>
-      <c r="B139" s="19">
-        <v>43466</v>
-      </c>
-      <c r="C139" t="s">
-        <v>410</v>
+        <v>729</v>
+      </c>
+      <c r="B139" t="s">
+        <v>948</v>
+      </c>
+      <c r="C139" s="19">
+        <v>40323</v>
       </c>
       <c r="D139" t="s">
-        <v>178</v>
+        <v>443</v>
       </c>
       <c r="E139" t="s">
-        <v>41</v>
+        <v>257</v>
       </c>
       <c r="F139" t="s">
-        <v>41</v>
+        <v>694</v>
       </c>
       <c r="G139" t="s">
         <v>42</v>
       </c>
-      <c r="H139">
-        <v>20</v>
-      </c>
+      <c r="H139" t="s">
+        <v>42</v>
+      </c>
+      <c r="I139" s="21"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J2:K31">
-    <sortCondition descending="1" ref="K2:K31"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K2:L31">
+    <sortCondition descending="1" ref="L2:L31"/>
   </sortState>
-  <conditionalFormatting sqref="C122:C135">
+  <conditionalFormatting sqref="D122:D135">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O113">
+  <conditionalFormatting sqref="O2:P113">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13466,9 +14258,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4070F33-2B00-4E83-8A67-6464C7D4DAC6}">
   <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -13497,7 +14289,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -13529,7 +14321,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -13549,7 +14341,7 @@
         <v>3</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G32" si="0">F3+E3+D3+B3</f>
+        <f t="shared" ref="G3:G31" si="0">F3+E3+D3+B3</f>
         <v>955</v>
       </c>
       <c r="H3">
@@ -13561,7 +14353,7 @@
         <v>6.6319444444444446</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -13593,7 +14385,7 @@
         <v>3.8194444444444446</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>210</v>
       </c>
@@ -13625,7 +14417,7 @@
         <v>3.5416666666666665</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>178</v>
       </c>
@@ -13657,7 +14449,7 @@
         <v>3.125</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>173</v>
       </c>
@@ -13689,7 +14481,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -13721,7 +14513,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -13753,7 +14545,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>108</v>
       </c>
@@ -13785,7 +14577,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>202</v>
       </c>
@@ -13817,7 +14609,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>306</v>
       </c>
@@ -13849,7 +14641,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>197</v>
       </c>
@@ -13881,7 +14673,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>336</v>
       </c>
@@ -13913,7 +14705,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>257</v>
       </c>
@@ -13945,7 +14737,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>369</v>
       </c>
@@ -13977,7 +14769,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>249</v>
       </c>
@@ -14009,7 +14801,7 @@
         <v>2.875</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -14041,7 +14833,7 @@
         <v>2.875</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>409</v>
       </c>
@@ -14073,7 +14865,7 @@
         <v>2.875</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>119</v>
       </c>
@@ -14105,7 +14897,7 @@
         <v>2.5625</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>156</v>
       </c>
@@ -14137,7 +14929,7 @@
         <v>2.40625</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>98</v>
       </c>
@@ -14169,7 +14961,7 @@
         <v>2.40625</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>442</v>
       </c>
@@ -14201,7 +14993,7 @@
         <v>2.09375</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>705</v>
       </c>
@@ -14233,7 +15025,7 @@
         <v>2.09375</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>352</v>
       </c>
@@ -14265,7 +15057,7 @@
         <v>1.9375</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>244</v>
       </c>
@@ -14297,7 +15089,7 @@
         <v>1.9375</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>488</v>
       </c>
@@ -14329,7 +15121,7 @@
         <v>1.78125</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>454</v>
       </c>
@@ -14361,7 +15153,7 @@
         <v>1.625</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>228</v>
       </c>
@@ -14393,7 +15185,7 @@
         <v>1.15625</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>278</v>
       </c>
@@ -14425,7 +15217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>298</v>
       </c>
